--- a/data/monthly_place/【2025年8月】月次配置.xlsx
+++ b/data/monthly_place/【2025年8月】月次配置.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="101">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -221,6 +221,108 @@
   </si>
   <si>
     <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Dining Bar Lien】...</t>
+  </si>
+  <si>
+    <t>デスクトップ</t>
+  </si>
+  <si>
+    <t>1日</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼ドキドキ💓はじめてのスポーツ体験！／...</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼2〜3歳のお子さまも大歓迎👶✨／...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍町寿司いちもんめ｜福井市大手...</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌸【女性クリニック ラポール】🌸
+すべての世代の女性に、安心と寄り添いを。...</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【髙橋歯科】
+“噛み合わせ”から整える、お口とカラダのトータルケア🪥...</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍Wild Crepes - ワイルドクレープス
+安い！旨い！多い！🎉...</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍸【bar moon walk 三条木屋町店】🌙...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶【駕町 とくさ】熊本・花畑町駅 徒歩5分...</t>
+  </si>
+  <si>
+    <t>炭焼　猿一</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>島田屋　東苗穂店</t>
+  </si>
+  <si>
+    <t>居ZAKKU　CHENOWA</t>
+  </si>
+  <si>
+    <t>三千段の民宿　幸登里</t>
+  </si>
+  <si>
+    <t>てんぐ屋</t>
+  </si>
+  <si>
+    <t>炭火焼肉友丸</t>
+  </si>
+  <si>
+    <t>旬彩屋　笑味</t>
+  </si>
+  <si>
+    <t>有限会社　大嶋_うまか喰い処 祇園 大しま</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【海鮮と肉料理 ほっかい酒房】🍣🍢✨
+すすきの駅から徒歩3分🚶‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【🦷アキュラデンタルクリニック🦷】...</t>
+  </si>
+  <si>
+    <t>archived</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【せがわ歯科クリニック】です🦷✨...</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
   </si>
 </sst>
 </file>
@@ -570,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB88"/>
+  <dimension ref="A1:AB206"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
@@ -7044,6 +7146,8438 @@
       </c>
       <c r="AB88">
         <v>65.400000000000006</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>38</v>
+      </c>
+      <c r="B89" t="s">
+        <v>37</v>
+      </c>
+      <c r="C89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" t="s">
+        <v>70</v>
+      </c>
+      <c r="G89" t="s">
+        <v>32</v>
+      </c>
+      <c r="H89" t="s">
+        <v>31</v>
+      </c>
+      <c r="K89">
+        <v>3</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>160</v>
+      </c>
+      <c r="O89" t="s">
+        <v>71</v>
+      </c>
+      <c r="P89">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>72</v>
+      </c>
+      <c r="R89">
+        <v>3</v>
+      </c>
+      <c r="S89">
+        <v>333.33333299999998</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+      <c r="Y89">
+        <v>0</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>38</v>
+      </c>
+      <c r="B90" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" t="s">
+        <v>43</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>32</v>
+      </c>
+      <c r="H90" t="s">
+        <v>31</v>
+      </c>
+      <c r="I90">
+        <v>45</v>
+      </c>
+      <c r="J90" t="s">
+        <v>30</v>
+      </c>
+      <c r="K90">
+        <v>1533</v>
+      </c>
+      <c r="L90">
+        <v>1.5198959999999999</v>
+      </c>
+      <c r="M90">
+        <v>31.533333330000001</v>
+      </c>
+      <c r="N90">
+        <v>160</v>
+      </c>
+      <c r="O90" t="s">
+        <v>71</v>
+      </c>
+      <c r="P90">
+        <v>1419</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>72</v>
+      </c>
+      <c r="R90">
+        <v>2330</v>
+      </c>
+      <c r="S90">
+        <v>609.01287600000001</v>
+      </c>
+      <c r="T90">
+        <v>45</v>
+      </c>
+      <c r="V90">
+        <v>31.533332999999999</v>
+      </c>
+      <c r="W90">
+        <v>1.93133</v>
+      </c>
+      <c r="X90">
+        <v>57</v>
+      </c>
+      <c r="Y90">
+        <v>2.4463520000000001</v>
+      </c>
+      <c r="Z90">
+        <v>24.894736999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>38</v>
+      </c>
+      <c r="B91" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91" t="s">
+        <v>69</v>
+      </c>
+      <c r="D91" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" t="s">
+        <v>43</v>
+      </c>
+      <c r="F91" t="s">
+        <v>46</v>
+      </c>
+      <c r="G91" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91" t="s">
+        <v>31</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="N91">
+        <v>160</v>
+      </c>
+      <c r="O91" t="s">
+        <v>71</v>
+      </c>
+      <c r="P91">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>72</v>
+      </c>
+      <c r="R91">
+        <v>1</v>
+      </c>
+      <c r="S91">
+        <v>1000</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+      <c r="Y91">
+        <v>0</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>38</v>
+      </c>
+      <c r="B92" t="s">
+        <v>37</v>
+      </c>
+      <c r="C92" t="s">
+        <v>69</v>
+      </c>
+      <c r="D92" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" t="s">
+        <v>33</v>
+      </c>
+      <c r="G92" t="s">
+        <v>32</v>
+      </c>
+      <c r="H92" t="s">
+        <v>31</v>
+      </c>
+      <c r="I92">
+        <v>6</v>
+      </c>
+      <c r="J92" t="s">
+        <v>30</v>
+      </c>
+      <c r="K92">
+        <v>299</v>
+      </c>
+      <c r="L92">
+        <v>1.3545149999999999</v>
+      </c>
+      <c r="M92">
+        <v>22.833333329999999</v>
+      </c>
+      <c r="N92">
+        <v>160</v>
+      </c>
+      <c r="O92" t="s">
+        <v>71</v>
+      </c>
+      <c r="P92">
+        <v>137</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>72</v>
+      </c>
+      <c r="R92">
+        <v>405</v>
+      </c>
+      <c r="S92">
+        <v>338.27160500000002</v>
+      </c>
+      <c r="T92">
+        <v>6</v>
+      </c>
+      <c r="V92">
+        <v>22.833333</v>
+      </c>
+      <c r="W92">
+        <v>1.481481</v>
+      </c>
+      <c r="X92">
+        <v>10</v>
+      </c>
+      <c r="Y92">
+        <v>2.4691360000000002</v>
+      </c>
+      <c r="Z92">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>38</v>
+      </c>
+      <c r="B93" t="s">
+        <v>37</v>
+      </c>
+      <c r="C93" t="s">
+        <v>69</v>
+      </c>
+      <c r="D93" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" t="s">
+        <v>32</v>
+      </c>
+      <c r="H93" t="s">
+        <v>31</v>
+      </c>
+      <c r="K93">
+        <v>18</v>
+      </c>
+      <c r="L93">
+        <v>1.0555559999999999</v>
+      </c>
+      <c r="N93">
+        <v>160</v>
+      </c>
+      <c r="O93" t="s">
+        <v>71</v>
+      </c>
+      <c r="P93">
+        <v>2</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>72</v>
+      </c>
+      <c r="R93">
+        <v>19</v>
+      </c>
+      <c r="S93">
+        <v>105.263158</v>
+      </c>
+      <c r="X93">
+        <v>0</v>
+      </c>
+      <c r="Y93">
+        <v>0</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>38</v>
+      </c>
+      <c r="B94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C94" t="s">
+        <v>69</v>
+      </c>
+      <c r="D94" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" t="s">
+        <v>40</v>
+      </c>
+      <c r="F94" t="s">
+        <v>33</v>
+      </c>
+      <c r="G94" t="s">
+        <v>32</v>
+      </c>
+      <c r="H94" t="s">
+        <v>31</v>
+      </c>
+      <c r="I94">
+        <v>31</v>
+      </c>
+      <c r="J94" t="s">
+        <v>30</v>
+      </c>
+      <c r="K94">
+        <v>1136</v>
+      </c>
+      <c r="L94">
+        <v>1.4841549999999999</v>
+      </c>
+      <c r="M94">
+        <v>24.548387099999999</v>
+      </c>
+      <c r="N94">
+        <v>160</v>
+      </c>
+      <c r="O94" t="s">
+        <v>71</v>
+      </c>
+      <c r="P94">
+        <v>761</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>72</v>
+      </c>
+      <c r="R94">
+        <v>1686</v>
+      </c>
+      <c r="S94">
+        <v>451.36417599999999</v>
+      </c>
+      <c r="T94">
+        <v>31</v>
+      </c>
+      <c r="V94">
+        <v>24.548387000000002</v>
+      </c>
+      <c r="W94">
+        <v>1.8386709999999999</v>
+      </c>
+      <c r="X94">
+        <v>60</v>
+      </c>
+      <c r="Y94">
+        <v>3.558719</v>
+      </c>
+      <c r="Z94">
+        <v>12.683332999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>38</v>
+      </c>
+      <c r="B95" t="s">
+        <v>37</v>
+      </c>
+      <c r="C95" t="s">
+        <v>69</v>
+      </c>
+      <c r="D95" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" t="s">
+        <v>34</v>
+      </c>
+      <c r="F95" t="s">
+        <v>33</v>
+      </c>
+      <c r="G95" t="s">
+        <v>32</v>
+      </c>
+      <c r="H95" t="s">
+        <v>31</v>
+      </c>
+      <c r="I95">
+        <v>100</v>
+      </c>
+      <c r="J95" t="s">
+        <v>30</v>
+      </c>
+      <c r="K95">
+        <v>2591</v>
+      </c>
+      <c r="L95">
+        <v>1.4940180000000001</v>
+      </c>
+      <c r="M95">
+        <v>26.43</v>
+      </c>
+      <c r="N95">
+        <v>160</v>
+      </c>
+      <c r="O95" t="s">
+        <v>71</v>
+      </c>
+      <c r="P95">
+        <v>2643</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>72</v>
+      </c>
+      <c r="R95">
+        <v>3871</v>
+      </c>
+      <c r="S95">
+        <v>682.76931000000002</v>
+      </c>
+      <c r="T95">
+        <v>100</v>
+      </c>
+      <c r="V95">
+        <v>26.43</v>
+      </c>
+      <c r="W95">
+        <v>2.5833119999999998</v>
+      </c>
+      <c r="X95">
+        <v>145</v>
+      </c>
+      <c r="Y95">
+        <v>3.7458019999999999</v>
+      </c>
+      <c r="Z95">
+        <v>18.227585999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>38</v>
+      </c>
+      <c r="B96" t="s">
+        <v>37</v>
+      </c>
+      <c r="C96" t="s">
+        <v>73</v>
+      </c>
+      <c r="D96" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G96" t="s">
+        <v>48</v>
+      </c>
+      <c r="H96" t="s">
+        <v>31</v>
+      </c>
+      <c r="I96">
+        <v>12</v>
+      </c>
+      <c r="J96" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96">
+        <v>308</v>
+      </c>
+      <c r="L96">
+        <v>1.353896</v>
+      </c>
+      <c r="M96">
+        <v>33.416666669999998</v>
+      </c>
+      <c r="N96">
+        <v>160</v>
+      </c>
+      <c r="O96" t="s">
+        <v>71</v>
+      </c>
+      <c r="P96">
+        <v>401</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>74</v>
+      </c>
+      <c r="R96">
+        <v>417</v>
+      </c>
+      <c r="S96">
+        <v>961.63069499999995</v>
+      </c>
+      <c r="T96">
+        <v>12</v>
+      </c>
+      <c r="V96">
+        <v>33.416666999999997</v>
+      </c>
+      <c r="W96">
+        <v>2.8776980000000001</v>
+      </c>
+      <c r="X96">
+        <v>13</v>
+      </c>
+      <c r="Y96">
+        <v>3.1175060000000001</v>
+      </c>
+      <c r="Z96">
+        <v>30.846153999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>38</v>
+      </c>
+      <c r="B97" t="s">
+        <v>37</v>
+      </c>
+      <c r="C97" t="s">
+        <v>73</v>
+      </c>
+      <c r="D97" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" t="s">
+        <v>33</v>
+      </c>
+      <c r="G97" t="s">
+        <v>48</v>
+      </c>
+      <c r="H97" t="s">
+        <v>31</v>
+      </c>
+      <c r="K97">
+        <v>14</v>
+      </c>
+      <c r="L97">
+        <v>1.428571</v>
+      </c>
+      <c r="N97">
+        <v>160</v>
+      </c>
+      <c r="O97" t="s">
+        <v>71</v>
+      </c>
+      <c r="P97">
+        <v>11</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>74</v>
+      </c>
+      <c r="R97">
+        <v>20</v>
+      </c>
+      <c r="S97">
+        <v>550</v>
+      </c>
+      <c r="X97">
+        <v>0</v>
+      </c>
+      <c r="Y97">
+        <v>0</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>38</v>
+      </c>
+      <c r="B98" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98" t="s">
+        <v>73</v>
+      </c>
+      <c r="D98" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" t="s">
+        <v>40</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98" t="s">
+        <v>48</v>
+      </c>
+      <c r="H98" t="s">
+        <v>31</v>
+      </c>
+      <c r="I98">
+        <v>15</v>
+      </c>
+      <c r="J98" t="s">
+        <v>30</v>
+      </c>
+      <c r="K98">
+        <v>328</v>
+      </c>
+      <c r="L98">
+        <v>1.304878</v>
+      </c>
+      <c r="M98">
+        <v>21.266666669999999</v>
+      </c>
+      <c r="N98">
+        <v>160</v>
+      </c>
+      <c r="O98" t="s">
+        <v>71</v>
+      </c>
+      <c r="P98">
+        <v>319</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>74</v>
+      </c>
+      <c r="R98">
+        <v>428</v>
+      </c>
+      <c r="S98">
+        <v>745.32710299999997</v>
+      </c>
+      <c r="T98">
+        <v>15</v>
+      </c>
+      <c r="V98">
+        <v>21.266667000000002</v>
+      </c>
+      <c r="W98">
+        <v>3.5046729999999999</v>
+      </c>
+      <c r="X98">
+        <v>18</v>
+      </c>
+      <c r="Y98">
+        <v>4.2056069999999997</v>
+      </c>
+      <c r="Z98">
+        <v>17.722221999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>38</v>
+      </c>
+      <c r="B99" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99" t="s">
+        <v>73</v>
+      </c>
+      <c r="D99" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" t="s">
+        <v>34</v>
+      </c>
+      <c r="F99" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" t="s">
+        <v>48</v>
+      </c>
+      <c r="H99" t="s">
+        <v>31</v>
+      </c>
+      <c r="I99">
+        <v>96</v>
+      </c>
+      <c r="J99" t="s">
+        <v>30</v>
+      </c>
+      <c r="K99">
+        <v>5774</v>
+      </c>
+      <c r="L99">
+        <v>1.203152</v>
+      </c>
+      <c r="M99">
+        <v>44.15625</v>
+      </c>
+      <c r="N99">
+        <v>160</v>
+      </c>
+      <c r="O99" t="s">
+        <v>71</v>
+      </c>
+      <c r="P99">
+        <v>4239</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>74</v>
+      </c>
+      <c r="R99">
+        <v>6947</v>
+      </c>
+      <c r="S99">
+        <v>610.19145000000003</v>
+      </c>
+      <c r="T99">
+        <v>96</v>
+      </c>
+      <c r="V99">
+        <v>44.15625</v>
+      </c>
+      <c r="W99">
+        <v>1.381891</v>
+      </c>
+      <c r="X99">
+        <v>104</v>
+      </c>
+      <c r="Y99">
+        <v>1.4970490000000001</v>
+      </c>
+      <c r="Z99">
+        <v>40.759614999999997</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100" t="s">
+        <v>37</v>
+      </c>
+      <c r="C100" t="s">
+        <v>75</v>
+      </c>
+      <c r="D100" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" t="s">
+        <v>43</v>
+      </c>
+      <c r="F100" t="s">
+        <v>70</v>
+      </c>
+      <c r="G100" t="s">
+        <v>48</v>
+      </c>
+      <c r="H100" t="s">
+        <v>31</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>160</v>
+      </c>
+      <c r="O100" t="s">
+        <v>71</v>
+      </c>
+      <c r="P100">
+        <v>2</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>74</v>
+      </c>
+      <c r="R100">
+        <v>1</v>
+      </c>
+      <c r="S100">
+        <v>2000</v>
+      </c>
+      <c r="X100">
+        <v>0</v>
+      </c>
+      <c r="Y100">
+        <v>0</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>38</v>
+      </c>
+      <c r="B101" t="s">
+        <v>37</v>
+      </c>
+      <c r="C101" t="s">
+        <v>75</v>
+      </c>
+      <c r="D101" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" t="s">
+        <v>43</v>
+      </c>
+      <c r="F101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" t="s">
+        <v>48</v>
+      </c>
+      <c r="H101" t="s">
+        <v>31</v>
+      </c>
+      <c r="I101">
+        <v>32</v>
+      </c>
+      <c r="J101" t="s">
+        <v>30</v>
+      </c>
+      <c r="K101">
+        <v>958</v>
+      </c>
+      <c r="L101">
+        <v>1.2818369999999999</v>
+      </c>
+      <c r="M101">
+        <v>25.71875</v>
+      </c>
+      <c r="N101">
+        <v>160</v>
+      </c>
+      <c r="O101" t="s">
+        <v>71</v>
+      </c>
+      <c r="P101">
+        <v>823</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>74</v>
+      </c>
+      <c r="R101">
+        <v>1228</v>
+      </c>
+      <c r="S101">
+        <v>670.19543999999996</v>
+      </c>
+      <c r="T101">
+        <v>32</v>
+      </c>
+      <c r="V101">
+        <v>25.71875</v>
+      </c>
+      <c r="W101">
+        <v>2.6058629999999998</v>
+      </c>
+      <c r="X101">
+        <v>41</v>
+      </c>
+      <c r="Y101">
+        <v>3.338762</v>
+      </c>
+      <c r="Z101">
+        <v>20.073170999999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>38</v>
+      </c>
+      <c r="B102" t="s">
+        <v>37</v>
+      </c>
+      <c r="C102" t="s">
+        <v>75</v>
+      </c>
+      <c r="D102" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" t="s">
+        <v>33</v>
+      </c>
+      <c r="G102" t="s">
+        <v>48</v>
+      </c>
+      <c r="H102" t="s">
+        <v>31</v>
+      </c>
+      <c r="I102">
+        <v>4</v>
+      </c>
+      <c r="J102" t="s">
+        <v>30</v>
+      </c>
+      <c r="K102">
+        <v>158</v>
+      </c>
+      <c r="L102">
+        <v>1.2531650000000001</v>
+      </c>
+      <c r="M102">
+        <v>17</v>
+      </c>
+      <c r="N102">
+        <v>160</v>
+      </c>
+      <c r="O102" t="s">
+        <v>71</v>
+      </c>
+      <c r="P102">
+        <v>68</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>74</v>
+      </c>
+      <c r="R102">
+        <v>198</v>
+      </c>
+      <c r="S102">
+        <v>343.43434300000001</v>
+      </c>
+      <c r="T102">
+        <v>4</v>
+      </c>
+      <c r="V102">
+        <v>17</v>
+      </c>
+      <c r="W102">
+        <v>2.0202019999999998</v>
+      </c>
+      <c r="X102">
+        <v>4</v>
+      </c>
+      <c r="Y102">
+        <v>2.0202019999999998</v>
+      </c>
+      <c r="Z102">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>38</v>
+      </c>
+      <c r="B103" t="s">
+        <v>37</v>
+      </c>
+      <c r="C103" t="s">
+        <v>75</v>
+      </c>
+      <c r="D103" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" t="s">
+        <v>41</v>
+      </c>
+      <c r="F103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" t="s">
+        <v>48</v>
+      </c>
+      <c r="H103" t="s">
+        <v>31</v>
+      </c>
+      <c r="K103">
+        <v>42</v>
+      </c>
+      <c r="L103">
+        <v>1.214286</v>
+      </c>
+      <c r="N103">
+        <v>160</v>
+      </c>
+      <c r="O103" t="s">
+        <v>71</v>
+      </c>
+      <c r="P103">
+        <v>7</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>74</v>
+      </c>
+      <c r="R103">
+        <v>51</v>
+      </c>
+      <c r="S103">
+        <v>137.25490199999999</v>
+      </c>
+      <c r="X103">
+        <v>1</v>
+      </c>
+      <c r="Y103">
+        <v>1.9607840000000001</v>
+      </c>
+      <c r="Z103">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>38</v>
+      </c>
+      <c r="B104" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" t="s">
+        <v>75</v>
+      </c>
+      <c r="D104" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" t="s">
+        <v>40</v>
+      </c>
+      <c r="F104" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104" t="s">
+        <v>48</v>
+      </c>
+      <c r="H104" t="s">
+        <v>31</v>
+      </c>
+      <c r="I104">
+        <v>8</v>
+      </c>
+      <c r="J104" t="s">
+        <v>30</v>
+      </c>
+      <c r="K104">
+        <v>376</v>
+      </c>
+      <c r="L104">
+        <v>1.103723</v>
+      </c>
+      <c r="M104">
+        <v>25.125</v>
+      </c>
+      <c r="N104">
+        <v>160</v>
+      </c>
+      <c r="O104" t="s">
+        <v>71</v>
+      </c>
+      <c r="P104">
+        <v>201</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>74</v>
+      </c>
+      <c r="R104">
+        <v>415</v>
+      </c>
+      <c r="S104">
+        <v>484.33734900000002</v>
+      </c>
+      <c r="T104">
+        <v>8</v>
+      </c>
+      <c r="V104">
+        <v>25.125</v>
+      </c>
+      <c r="W104">
+        <v>1.927711</v>
+      </c>
+      <c r="X104">
+        <v>11</v>
+      </c>
+      <c r="Y104">
+        <v>2.6506020000000001</v>
+      </c>
+      <c r="Z104">
+        <v>18.272727</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>38</v>
+      </c>
+      <c r="B105" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" t="s">
+        <v>75</v>
+      </c>
+      <c r="D105" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" t="s">
+        <v>34</v>
+      </c>
+      <c r="F105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105" t="s">
+        <v>48</v>
+      </c>
+      <c r="H105" t="s">
+        <v>31</v>
+      </c>
+      <c r="I105">
+        <v>203</v>
+      </c>
+      <c r="J105" t="s">
+        <v>30</v>
+      </c>
+      <c r="K105">
+        <v>3952</v>
+      </c>
+      <c r="L105">
+        <v>1.2462040000000001</v>
+      </c>
+      <c r="M105">
+        <v>19</v>
+      </c>
+      <c r="N105">
+        <v>160</v>
+      </c>
+      <c r="O105" t="s">
+        <v>71</v>
+      </c>
+      <c r="P105">
+        <v>3857</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>74</v>
+      </c>
+      <c r="R105">
+        <v>4925</v>
+      </c>
+      <c r="S105">
+        <v>783.14720799999998</v>
+      </c>
+      <c r="T105">
+        <v>203</v>
+      </c>
+      <c r="V105">
+        <v>19</v>
+      </c>
+      <c r="W105">
+        <v>4.1218269999999997</v>
+      </c>
+      <c r="X105">
+        <v>276</v>
+      </c>
+      <c r="Y105">
+        <v>5.6040609999999997</v>
+      </c>
+      <c r="Z105">
+        <v>13.974638000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>38</v>
+      </c>
+      <c r="B106" t="s">
+        <v>37</v>
+      </c>
+      <c r="C106" t="s">
+        <v>76</v>
+      </c>
+      <c r="D106" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" t="s">
+        <v>43</v>
+      </c>
+      <c r="F106" t="s">
+        <v>70</v>
+      </c>
+      <c r="G106" t="s">
+        <v>48</v>
+      </c>
+      <c r="H106" t="s">
+        <v>31</v>
+      </c>
+      <c r="K106">
+        <v>4</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="N106">
+        <v>160</v>
+      </c>
+      <c r="O106" t="s">
+        <v>71</v>
+      </c>
+      <c r="P106">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>77</v>
+      </c>
+      <c r="R106">
+        <v>4</v>
+      </c>
+      <c r="S106">
+        <v>250</v>
+      </c>
+      <c r="X106">
+        <v>0</v>
+      </c>
+      <c r="Y106">
+        <v>0</v>
+      </c>
+      <c r="Z106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>38</v>
+      </c>
+      <c r="B107" t="s">
+        <v>37</v>
+      </c>
+      <c r="C107" t="s">
+        <v>76</v>
+      </c>
+      <c r="D107" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" t="s">
+        <v>43</v>
+      </c>
+      <c r="F107" t="s">
+        <v>33</v>
+      </c>
+      <c r="G107" t="s">
+        <v>48</v>
+      </c>
+      <c r="H107" t="s">
+        <v>31</v>
+      </c>
+      <c r="I107">
+        <v>95</v>
+      </c>
+      <c r="J107" t="s">
+        <v>30</v>
+      </c>
+      <c r="K107">
+        <v>1788</v>
+      </c>
+      <c r="L107">
+        <v>1.445749</v>
+      </c>
+      <c r="M107">
+        <v>29.115789469999999</v>
+      </c>
+      <c r="N107">
+        <v>160</v>
+      </c>
+      <c r="O107" t="s">
+        <v>71</v>
+      </c>
+      <c r="P107">
+        <v>2766</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>77</v>
+      </c>
+      <c r="R107">
+        <v>2585</v>
+      </c>
+      <c r="S107">
+        <v>1070.0193420000001</v>
+      </c>
+      <c r="T107">
+        <v>95</v>
+      </c>
+      <c r="V107">
+        <v>29.115788999999999</v>
+      </c>
+      <c r="W107">
+        <v>3.6750479999999999</v>
+      </c>
+      <c r="X107">
+        <v>101</v>
+      </c>
+      <c r="Y107">
+        <v>3.9071570000000002</v>
+      </c>
+      <c r="Z107">
+        <v>27.386139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>38</v>
+      </c>
+      <c r="B108" t="s">
+        <v>37</v>
+      </c>
+      <c r="C108" t="s">
+        <v>76</v>
+      </c>
+      <c r="D108" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" t="s">
+        <v>46</v>
+      </c>
+      <c r="G108" t="s">
+        <v>48</v>
+      </c>
+      <c r="H108" t="s">
+        <v>31</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>160</v>
+      </c>
+      <c r="O108" t="s">
+        <v>71</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>77</v>
+      </c>
+      <c r="R108">
+        <v>1</v>
+      </c>
+      <c r="S108">
+        <v>0</v>
+      </c>
+      <c r="X108">
+        <v>0</v>
+      </c>
+      <c r="Y108">
+        <v>0</v>
+      </c>
+      <c r="Z108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>38</v>
+      </c>
+      <c r="B109" t="s">
+        <v>37</v>
+      </c>
+      <c r="C109" t="s">
+        <v>76</v>
+      </c>
+      <c r="D109" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" t="s">
+        <v>33</v>
+      </c>
+      <c r="G109" t="s">
+        <v>48</v>
+      </c>
+      <c r="H109" t="s">
+        <v>31</v>
+      </c>
+      <c r="I109">
+        <v>5</v>
+      </c>
+      <c r="J109" t="s">
+        <v>30</v>
+      </c>
+      <c r="K109">
+        <v>218</v>
+      </c>
+      <c r="L109">
+        <v>1.3027519999999999</v>
+      </c>
+      <c r="M109">
+        <v>20.8</v>
+      </c>
+      <c r="N109">
+        <v>160</v>
+      </c>
+      <c r="O109" t="s">
+        <v>71</v>
+      </c>
+      <c r="P109">
+        <v>104</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>77</v>
+      </c>
+      <c r="R109">
+        <v>284</v>
+      </c>
+      <c r="S109">
+        <v>366.197183</v>
+      </c>
+      <c r="T109">
+        <v>5</v>
+      </c>
+      <c r="V109">
+        <v>20.8</v>
+      </c>
+      <c r="W109">
+        <v>1.7605630000000001</v>
+      </c>
+      <c r="X109">
+        <v>6</v>
+      </c>
+      <c r="Y109">
+        <v>2.112676</v>
+      </c>
+      <c r="Z109">
+        <v>17.333333</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>38</v>
+      </c>
+      <c r="B110" t="s">
+        <v>37</v>
+      </c>
+      <c r="C110" t="s">
+        <v>76</v>
+      </c>
+      <c r="D110" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" t="s">
+        <v>41</v>
+      </c>
+      <c r="F110" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" t="s">
+        <v>48</v>
+      </c>
+      <c r="H110" t="s">
+        <v>31</v>
+      </c>
+      <c r="K110">
+        <v>7</v>
+      </c>
+      <c r="L110">
+        <v>1.142857</v>
+      </c>
+      <c r="N110">
+        <v>160</v>
+      </c>
+      <c r="O110" t="s">
+        <v>71</v>
+      </c>
+      <c r="P110">
+        <v>2</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>77</v>
+      </c>
+      <c r="R110">
+        <v>8</v>
+      </c>
+      <c r="S110">
+        <v>250</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>0</v>
+      </c>
+      <c r="Z110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>38</v>
+      </c>
+      <c r="B111" t="s">
+        <v>37</v>
+      </c>
+      <c r="C111" t="s">
+        <v>76</v>
+      </c>
+      <c r="D111" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" t="s">
+        <v>40</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111" t="s">
+        <v>48</v>
+      </c>
+      <c r="H111" t="s">
+        <v>31</v>
+      </c>
+      <c r="I111">
+        <v>10</v>
+      </c>
+      <c r="J111" t="s">
+        <v>30</v>
+      </c>
+      <c r="K111">
+        <v>198</v>
+      </c>
+      <c r="L111">
+        <v>1.1464650000000001</v>
+      </c>
+      <c r="M111">
+        <v>14.2</v>
+      </c>
+      <c r="N111">
+        <v>160</v>
+      </c>
+      <c r="O111" t="s">
+        <v>71</v>
+      </c>
+      <c r="P111">
+        <v>142</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>77</v>
+      </c>
+      <c r="R111">
+        <v>227</v>
+      </c>
+      <c r="S111">
+        <v>625.55066099999999</v>
+      </c>
+      <c r="T111">
+        <v>10</v>
+      </c>
+      <c r="V111">
+        <v>14.2</v>
+      </c>
+      <c r="W111">
+        <v>4.4052860000000003</v>
+      </c>
+      <c r="X111">
+        <v>10</v>
+      </c>
+      <c r="Y111">
+        <v>4.4052860000000003</v>
+      </c>
+      <c r="Z111">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>38</v>
+      </c>
+      <c r="B112" t="s">
+        <v>37</v>
+      </c>
+      <c r="C112" t="s">
+        <v>76</v>
+      </c>
+      <c r="D112" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" t="s">
+        <v>34</v>
+      </c>
+      <c r="F112" t="s">
+        <v>33</v>
+      </c>
+      <c r="G112" t="s">
+        <v>48</v>
+      </c>
+      <c r="H112" t="s">
+        <v>31</v>
+      </c>
+      <c r="I112">
+        <v>115</v>
+      </c>
+      <c r="J112" t="s">
+        <v>30</v>
+      </c>
+      <c r="K112">
+        <v>1408</v>
+      </c>
+      <c r="L112">
+        <v>1.2784089999999999</v>
+      </c>
+      <c r="M112">
+        <v>16.956521739999999</v>
+      </c>
+      <c r="N112">
+        <v>160</v>
+      </c>
+      <c r="O112" t="s">
+        <v>71</v>
+      </c>
+      <c r="P112">
+        <v>1950</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>77</v>
+      </c>
+      <c r="R112">
+        <v>1800</v>
+      </c>
+      <c r="S112">
+        <v>1083.333333</v>
+      </c>
+      <c r="T112">
+        <v>115</v>
+      </c>
+      <c r="V112">
+        <v>16.956522</v>
+      </c>
+      <c r="W112">
+        <v>6.3888889999999998</v>
+      </c>
+      <c r="X112">
+        <v>129</v>
+      </c>
+      <c r="Y112">
+        <v>7.1666670000000003</v>
+      </c>
+      <c r="Z112">
+        <v>15.116279</v>
+      </c>
+    </row>
+    <row r="113" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>38</v>
+      </c>
+      <c r="B113" t="s">
+        <v>37</v>
+      </c>
+      <c r="C113" t="s">
+        <v>78</v>
+      </c>
+      <c r="D113" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" t="s">
+        <v>43</v>
+      </c>
+      <c r="F113" t="s">
+        <v>70</v>
+      </c>
+      <c r="G113" t="s">
+        <v>32</v>
+      </c>
+      <c r="H113" t="s">
+        <v>31</v>
+      </c>
+      <c r="K113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="N113">
+        <v>160</v>
+      </c>
+      <c r="O113" t="s">
+        <v>71</v>
+      </c>
+      <c r="P113">
+        <v>2</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>79</v>
+      </c>
+      <c r="R113">
+        <v>1</v>
+      </c>
+      <c r="S113">
+        <v>2000</v>
+      </c>
+      <c r="X113">
+        <v>0</v>
+      </c>
+      <c r="Y113">
+        <v>0</v>
+      </c>
+      <c r="Z113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114" t="s">
+        <v>37</v>
+      </c>
+      <c r="C114" t="s">
+        <v>78</v>
+      </c>
+      <c r="D114" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" t="s">
+        <v>43</v>
+      </c>
+      <c r="F114" t="s">
+        <v>33</v>
+      </c>
+      <c r="G114" t="s">
+        <v>32</v>
+      </c>
+      <c r="H114" t="s">
+        <v>31</v>
+      </c>
+      <c r="I114">
+        <v>72</v>
+      </c>
+      <c r="J114" t="s">
+        <v>30</v>
+      </c>
+      <c r="K114">
+        <v>2118</v>
+      </c>
+      <c r="L114">
+        <v>1.511331</v>
+      </c>
+      <c r="M114">
+        <v>33.958333330000002</v>
+      </c>
+      <c r="N114">
+        <v>160</v>
+      </c>
+      <c r="O114" t="s">
+        <v>71</v>
+      </c>
+      <c r="P114">
+        <v>2445</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>79</v>
+      </c>
+      <c r="R114">
+        <v>3201</v>
+      </c>
+      <c r="S114">
+        <v>763.82380499999999</v>
+      </c>
+      <c r="T114">
+        <v>72</v>
+      </c>
+      <c r="V114">
+        <v>33.958333000000003</v>
+      </c>
+      <c r="W114">
+        <v>2.2492969999999999</v>
+      </c>
+      <c r="X114">
+        <v>86</v>
+      </c>
+      <c r="Y114">
+        <v>2.6866599999999998</v>
+      </c>
+      <c r="Z114">
+        <v>28.430233000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>38</v>
+      </c>
+      <c r="B115" t="s">
+        <v>37</v>
+      </c>
+      <c r="C115" t="s">
+        <v>78</v>
+      </c>
+      <c r="D115" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" t="s">
+        <v>42</v>
+      </c>
+      <c r="F115" t="s">
+        <v>33</v>
+      </c>
+      <c r="G115" t="s">
+        <v>32</v>
+      </c>
+      <c r="H115" t="s">
+        <v>31</v>
+      </c>
+      <c r="I115">
+        <v>12</v>
+      </c>
+      <c r="J115" t="s">
+        <v>30</v>
+      </c>
+      <c r="K115">
+        <v>429</v>
+      </c>
+      <c r="L115">
+        <v>1.417249</v>
+      </c>
+      <c r="M115">
+        <v>24.75</v>
+      </c>
+      <c r="N115">
+        <v>160</v>
+      </c>
+      <c r="O115" t="s">
+        <v>71</v>
+      </c>
+      <c r="P115">
+        <v>297</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>79</v>
+      </c>
+      <c r="R115">
+        <v>608</v>
+      </c>
+      <c r="S115">
+        <v>488.48684200000002</v>
+      </c>
+      <c r="T115">
+        <v>12</v>
+      </c>
+      <c r="V115">
+        <v>24.75</v>
+      </c>
+      <c r="W115">
+        <v>1.973684</v>
+      </c>
+      <c r="X115">
+        <v>13</v>
+      </c>
+      <c r="Y115">
+        <v>2.1381579999999998</v>
+      </c>
+      <c r="Z115">
+        <v>22.846153999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>38</v>
+      </c>
+      <c r="B116" t="s">
+        <v>37</v>
+      </c>
+      <c r="C116" t="s">
+        <v>78</v>
+      </c>
+      <c r="D116" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" t="s">
+        <v>41</v>
+      </c>
+      <c r="F116" t="s">
+        <v>33</v>
+      </c>
+      <c r="G116" t="s">
+        <v>32</v>
+      </c>
+      <c r="H116" t="s">
+        <v>31</v>
+      </c>
+      <c r="K116">
+        <v>16</v>
+      </c>
+      <c r="L116">
+        <v>1.125</v>
+      </c>
+      <c r="N116">
+        <v>160</v>
+      </c>
+      <c r="O116" t="s">
+        <v>71</v>
+      </c>
+      <c r="P116">
+        <v>4</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>79</v>
+      </c>
+      <c r="R116">
+        <v>18</v>
+      </c>
+      <c r="S116">
+        <v>222.22222199999999</v>
+      </c>
+      <c r="X116">
+        <v>0</v>
+      </c>
+      <c r="Y116">
+        <v>0</v>
+      </c>
+      <c r="Z116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>38</v>
+      </c>
+      <c r="B117" t="s">
+        <v>37</v>
+      </c>
+      <c r="C117" t="s">
+        <v>78</v>
+      </c>
+      <c r="D117" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" t="s">
+        <v>40</v>
+      </c>
+      <c r="F117" t="s">
+        <v>33</v>
+      </c>
+      <c r="G117" t="s">
+        <v>32</v>
+      </c>
+      <c r="H117" t="s">
+        <v>31</v>
+      </c>
+      <c r="I117">
+        <v>49</v>
+      </c>
+      <c r="J117" t="s">
+        <v>30</v>
+      </c>
+      <c r="K117">
+        <v>1386</v>
+      </c>
+      <c r="L117">
+        <v>1.4300139999999999</v>
+      </c>
+      <c r="M117">
+        <v>32.795918370000003</v>
+      </c>
+      <c r="N117">
+        <v>160</v>
+      </c>
+      <c r="O117" t="s">
+        <v>71</v>
+      </c>
+      <c r="P117">
+        <v>1607</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>79</v>
+      </c>
+      <c r="R117">
+        <v>1982</v>
+      </c>
+      <c r="S117">
+        <v>810.79717500000004</v>
+      </c>
+      <c r="T117">
+        <v>49</v>
+      </c>
+      <c r="V117">
+        <v>32.795918</v>
+      </c>
+      <c r="W117">
+        <v>2.4722499999999998</v>
+      </c>
+      <c r="X117">
+        <v>61</v>
+      </c>
+      <c r="Y117">
+        <v>3.077699</v>
+      </c>
+      <c r="Z117">
+        <v>26.344262000000001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>38</v>
+      </c>
+      <c r="B118" t="s">
+        <v>37</v>
+      </c>
+      <c r="C118" t="s">
+        <v>78</v>
+      </c>
+      <c r="D118" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" t="s">
+        <v>34</v>
+      </c>
+      <c r="F118" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" t="s">
+        <v>32</v>
+      </c>
+      <c r="H118" t="s">
+        <v>31</v>
+      </c>
+      <c r="I118">
+        <v>17</v>
+      </c>
+      <c r="J118" t="s">
+        <v>30</v>
+      </c>
+      <c r="K118">
+        <v>367</v>
+      </c>
+      <c r="L118">
+        <v>1.280654</v>
+      </c>
+      <c r="M118">
+        <v>35.823529409999999</v>
+      </c>
+      <c r="N118">
+        <v>160</v>
+      </c>
+      <c r="O118" t="s">
+        <v>71</v>
+      </c>
+      <c r="P118">
+        <v>609</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>79</v>
+      </c>
+      <c r="R118">
+        <v>470</v>
+      </c>
+      <c r="S118">
+        <v>1295.7446809999999</v>
+      </c>
+      <c r="T118">
+        <v>17</v>
+      </c>
+      <c r="V118">
+        <v>35.823529000000001</v>
+      </c>
+      <c r="W118">
+        <v>3.6170209999999998</v>
+      </c>
+      <c r="X118">
+        <v>20</v>
+      </c>
+      <c r="Y118">
+        <v>4.2553190000000001</v>
+      </c>
+      <c r="Z118">
+        <v>30.45</v>
+      </c>
+    </row>
+    <row r="119" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>38</v>
+      </c>
+      <c r="B119" t="s">
+        <v>37</v>
+      </c>
+      <c r="C119" t="s">
+        <v>80</v>
+      </c>
+      <c r="D119" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" t="s">
+        <v>43</v>
+      </c>
+      <c r="F119" t="s">
+        <v>70</v>
+      </c>
+      <c r="G119" t="s">
+        <v>48</v>
+      </c>
+      <c r="H119" t="s">
+        <v>31</v>
+      </c>
+      <c r="K119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="N119">
+        <v>160</v>
+      </c>
+      <c r="O119" t="s">
+        <v>71</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>81</v>
+      </c>
+      <c r="R119">
+        <v>1</v>
+      </c>
+      <c r="S119">
+        <v>0</v>
+      </c>
+      <c r="X119">
+        <v>0</v>
+      </c>
+      <c r="Y119">
+        <v>0</v>
+      </c>
+      <c r="Z119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>38</v>
+      </c>
+      <c r="B120" t="s">
+        <v>37</v>
+      </c>
+      <c r="C120" t="s">
+        <v>80</v>
+      </c>
+      <c r="D120" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" t="s">
+        <v>43</v>
+      </c>
+      <c r="F120" t="s">
+        <v>33</v>
+      </c>
+      <c r="G120" t="s">
+        <v>48</v>
+      </c>
+      <c r="H120" t="s">
+        <v>31</v>
+      </c>
+      <c r="I120">
+        <v>17</v>
+      </c>
+      <c r="J120" t="s">
+        <v>30</v>
+      </c>
+      <c r="K120">
+        <v>591</v>
+      </c>
+      <c r="L120">
+        <v>1.338409</v>
+      </c>
+      <c r="M120">
+        <v>38.41176471</v>
+      </c>
+      <c r="N120">
+        <v>160</v>
+      </c>
+      <c r="O120" t="s">
+        <v>71</v>
+      </c>
+      <c r="P120">
+        <v>653</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>81</v>
+      </c>
+      <c r="R120">
+        <v>791</v>
+      </c>
+      <c r="S120">
+        <v>825.53729499999997</v>
+      </c>
+      <c r="T120">
+        <v>17</v>
+      </c>
+      <c r="V120">
+        <v>38.411765000000003</v>
+      </c>
+      <c r="W120">
+        <v>2.149178</v>
+      </c>
+      <c r="X120">
+        <v>18</v>
+      </c>
+      <c r="Y120">
+        <v>2.275601</v>
+      </c>
+      <c r="Z120">
+        <v>36.277777999999998</v>
+      </c>
+    </row>
+    <row r="121" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>38</v>
+      </c>
+      <c r="B121" t="s">
+        <v>37</v>
+      </c>
+      <c r="C121" t="s">
+        <v>80</v>
+      </c>
+      <c r="D121" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" t="s">
+        <v>43</v>
+      </c>
+      <c r="F121" t="s">
+        <v>46</v>
+      </c>
+      <c r="G121" t="s">
+        <v>48</v>
+      </c>
+      <c r="H121" t="s">
+        <v>31</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>160</v>
+      </c>
+      <c r="O121" t="s">
+        <v>71</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>81</v>
+      </c>
+      <c r="R121">
+        <v>1</v>
+      </c>
+      <c r="S121">
+        <v>0</v>
+      </c>
+      <c r="X121">
+        <v>0</v>
+      </c>
+      <c r="Y121">
+        <v>0</v>
+      </c>
+      <c r="Z121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>38</v>
+      </c>
+      <c r="B122" t="s">
+        <v>37</v>
+      </c>
+      <c r="C122" t="s">
+        <v>80</v>
+      </c>
+      <c r="D122" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" t="s">
+        <v>33</v>
+      </c>
+      <c r="G122" t="s">
+        <v>48</v>
+      </c>
+      <c r="H122" t="s">
+        <v>31</v>
+      </c>
+      <c r="I122">
+        <v>5</v>
+      </c>
+      <c r="J122" t="s">
+        <v>30</v>
+      </c>
+      <c r="K122">
+        <v>332</v>
+      </c>
+      <c r="L122">
+        <v>1.2259040000000001</v>
+      </c>
+      <c r="M122">
+        <v>43.4</v>
+      </c>
+      <c r="N122">
+        <v>160</v>
+      </c>
+      <c r="O122" t="s">
+        <v>71</v>
+      </c>
+      <c r="P122">
+        <v>217</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>81</v>
+      </c>
+      <c r="R122">
+        <v>407</v>
+      </c>
+      <c r="S122">
+        <v>533.169533</v>
+      </c>
+      <c r="T122">
+        <v>5</v>
+      </c>
+      <c r="V122">
+        <v>43.4</v>
+      </c>
+      <c r="W122">
+        <v>1.2285010000000001</v>
+      </c>
+      <c r="X122">
+        <v>6</v>
+      </c>
+      <c r="Y122">
+        <v>1.4742010000000001</v>
+      </c>
+      <c r="Z122">
+        <v>36.166666999999997</v>
+      </c>
+    </row>
+    <row r="123" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>38</v>
+      </c>
+      <c r="B123" t="s">
+        <v>37</v>
+      </c>
+      <c r="C123" t="s">
+        <v>80</v>
+      </c>
+      <c r="D123" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" t="s">
+        <v>41</v>
+      </c>
+      <c r="F123" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123" t="s">
+        <v>48</v>
+      </c>
+      <c r="H123" t="s">
+        <v>31</v>
+      </c>
+      <c r="K123">
+        <v>47</v>
+      </c>
+      <c r="L123">
+        <v>1.191489</v>
+      </c>
+      <c r="N123">
+        <v>160</v>
+      </c>
+      <c r="O123" t="s">
+        <v>71</v>
+      </c>
+      <c r="P123">
+        <v>12</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>81</v>
+      </c>
+      <c r="R123">
+        <v>56</v>
+      </c>
+      <c r="S123">
+        <v>214.28571400000001</v>
+      </c>
+      <c r="X123">
+        <v>1</v>
+      </c>
+      <c r="Y123">
+        <v>1.785714</v>
+      </c>
+      <c r="Z123">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>38</v>
+      </c>
+      <c r="B124" t="s">
+        <v>37</v>
+      </c>
+      <c r="C124" t="s">
+        <v>80</v>
+      </c>
+      <c r="D124" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" t="s">
+        <v>40</v>
+      </c>
+      <c r="F124" t="s">
+        <v>33</v>
+      </c>
+      <c r="G124" t="s">
+        <v>48</v>
+      </c>
+      <c r="H124" t="s">
+        <v>31</v>
+      </c>
+      <c r="I124">
+        <v>10</v>
+      </c>
+      <c r="J124" t="s">
+        <v>30</v>
+      </c>
+      <c r="K124">
+        <v>338</v>
+      </c>
+      <c r="L124">
+        <v>1.230769</v>
+      </c>
+      <c r="M124">
+        <v>29.9</v>
+      </c>
+      <c r="N124">
+        <v>160</v>
+      </c>
+      <c r="O124" t="s">
+        <v>71</v>
+      </c>
+      <c r="P124">
+        <v>299</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>81</v>
+      </c>
+      <c r="R124">
+        <v>416</v>
+      </c>
+      <c r="S124">
+        <v>718.75</v>
+      </c>
+      <c r="T124">
+        <v>10</v>
+      </c>
+      <c r="V124">
+        <v>29.9</v>
+      </c>
+      <c r="W124">
+        <v>2.4038460000000001</v>
+      </c>
+      <c r="X124">
+        <v>14</v>
+      </c>
+      <c r="Y124">
+        <v>3.3653849999999998</v>
+      </c>
+      <c r="Z124">
+        <v>21.357143000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>38</v>
+      </c>
+      <c r="B125" t="s">
+        <v>37</v>
+      </c>
+      <c r="C125" t="s">
+        <v>80</v>
+      </c>
+      <c r="D125" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" t="s">
+        <v>34</v>
+      </c>
+      <c r="F125" t="s">
+        <v>33</v>
+      </c>
+      <c r="G125" t="s">
+        <v>48</v>
+      </c>
+      <c r="H125" t="s">
+        <v>31</v>
+      </c>
+      <c r="I125">
+        <v>91</v>
+      </c>
+      <c r="J125" t="s">
+        <v>30</v>
+      </c>
+      <c r="K125">
+        <v>2073</v>
+      </c>
+      <c r="L125">
+        <v>1.347323</v>
+      </c>
+      <c r="M125">
+        <v>41.30769231</v>
+      </c>
+      <c r="N125">
+        <v>160</v>
+      </c>
+      <c r="O125" t="s">
+        <v>71</v>
+      </c>
+      <c r="P125">
+        <v>3759</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>81</v>
+      </c>
+      <c r="R125">
+        <v>2793</v>
+      </c>
+      <c r="S125">
+        <v>1345.864662</v>
+      </c>
+      <c r="T125">
+        <v>91</v>
+      </c>
+      <c r="V125">
+        <v>41.307692000000003</v>
+      </c>
+      <c r="W125">
+        <v>3.2581449999999998</v>
+      </c>
+      <c r="X125">
+        <v>102</v>
+      </c>
+      <c r="Y125">
+        <v>3.6519870000000001</v>
+      </c>
+      <c r="Z125">
+        <v>36.852941000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>38</v>
+      </c>
+      <c r="B126" t="s">
+        <v>37</v>
+      </c>
+      <c r="C126" t="s">
+        <v>82</v>
+      </c>
+      <c r="D126" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" t="s">
+        <v>43</v>
+      </c>
+      <c r="F126" t="s">
+        <v>70</v>
+      </c>
+      <c r="G126" t="s">
+        <v>32</v>
+      </c>
+      <c r="H126" t="s">
+        <v>31</v>
+      </c>
+      <c r="K126">
+        <v>6</v>
+      </c>
+      <c r="L126">
+        <v>1.1666669999999999</v>
+      </c>
+      <c r="N126">
+        <v>160</v>
+      </c>
+      <c r="O126" t="s">
+        <v>71</v>
+      </c>
+      <c r="P126">
+        <v>6</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>83</v>
+      </c>
+      <c r="R126">
+        <v>7</v>
+      </c>
+      <c r="S126">
+        <v>857.14285700000005</v>
+      </c>
+      <c r="X126">
+        <v>0</v>
+      </c>
+      <c r="Y126">
+        <v>0</v>
+      </c>
+      <c r="Z126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>38</v>
+      </c>
+      <c r="B127" t="s">
+        <v>37</v>
+      </c>
+      <c r="C127" t="s">
+        <v>82</v>
+      </c>
+      <c r="D127" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" t="s">
+        <v>43</v>
+      </c>
+      <c r="F127" t="s">
+        <v>33</v>
+      </c>
+      <c r="G127" t="s">
+        <v>32</v>
+      </c>
+      <c r="H127" t="s">
+        <v>31</v>
+      </c>
+      <c r="I127">
+        <v>175</v>
+      </c>
+      <c r="J127" t="s">
+        <v>30</v>
+      </c>
+      <c r="K127">
+        <v>3780</v>
+      </c>
+      <c r="L127">
+        <v>1.623016</v>
+      </c>
+      <c r="M127">
+        <v>17.068571429999999</v>
+      </c>
+      <c r="N127">
+        <v>160</v>
+      </c>
+      <c r="O127" t="s">
+        <v>71</v>
+      </c>
+      <c r="P127">
+        <v>2987</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>83</v>
+      </c>
+      <c r="R127">
+        <v>6135</v>
+      </c>
+      <c r="S127">
+        <v>486.87856599999998</v>
+      </c>
+      <c r="T127">
+        <v>175</v>
+      </c>
+      <c r="V127">
+        <v>17.068570999999999</v>
+      </c>
+      <c r="W127">
+        <v>2.8524859999999999</v>
+      </c>
+      <c r="X127">
+        <v>218</v>
+      </c>
+      <c r="Y127">
+        <v>3.553382</v>
+      </c>
+      <c r="Z127">
+        <v>13.701835000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>38</v>
+      </c>
+      <c r="B128" t="s">
+        <v>37</v>
+      </c>
+      <c r="C128" t="s">
+        <v>82</v>
+      </c>
+      <c r="D128" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" t="s">
+        <v>43</v>
+      </c>
+      <c r="F128" t="s">
+        <v>46</v>
+      </c>
+      <c r="G128" t="s">
+        <v>32</v>
+      </c>
+      <c r="H128" t="s">
+        <v>31</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>160</v>
+      </c>
+      <c r="O128" t="s">
+        <v>71</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>83</v>
+      </c>
+      <c r="R128">
+        <v>1</v>
+      </c>
+      <c r="S128">
+        <v>0</v>
+      </c>
+      <c r="X128">
+        <v>0</v>
+      </c>
+      <c r="Y128">
+        <v>0</v>
+      </c>
+      <c r="Z128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>38</v>
+      </c>
+      <c r="B129" t="s">
+        <v>37</v>
+      </c>
+      <c r="C129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D129" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129" t="s">
+        <v>33</v>
+      </c>
+      <c r="G129" t="s">
+        <v>32</v>
+      </c>
+      <c r="H129" t="s">
+        <v>31</v>
+      </c>
+      <c r="I129">
+        <v>12</v>
+      </c>
+      <c r="J129" t="s">
+        <v>30</v>
+      </c>
+      <c r="K129">
+        <v>500</v>
+      </c>
+      <c r="L129">
+        <v>1.484</v>
+      </c>
+      <c r="M129">
+        <v>24.416666670000001</v>
+      </c>
+      <c r="N129">
+        <v>160</v>
+      </c>
+      <c r="O129" t="s">
+        <v>71</v>
+      </c>
+      <c r="P129">
+        <v>293</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>83</v>
+      </c>
+      <c r="R129">
+        <v>742</v>
+      </c>
+      <c r="S129">
+        <v>394.87870600000002</v>
+      </c>
+      <c r="T129">
+        <v>12</v>
+      </c>
+      <c r="V129">
+        <v>24.416667</v>
+      </c>
+      <c r="W129">
+        <v>1.617251</v>
+      </c>
+      <c r="X129">
+        <v>16</v>
+      </c>
+      <c r="Y129">
+        <v>2.1563340000000002</v>
+      </c>
+      <c r="Z129">
+        <v>18.3125</v>
+      </c>
+    </row>
+    <row r="130" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>38</v>
+      </c>
+      <c r="B130" t="s">
+        <v>37</v>
+      </c>
+      <c r="C130" t="s">
+        <v>82</v>
+      </c>
+      <c r="D130" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" t="s">
+        <v>41</v>
+      </c>
+      <c r="F130" t="s">
+        <v>33</v>
+      </c>
+      <c r="G130" t="s">
+        <v>32</v>
+      </c>
+      <c r="H130" t="s">
+        <v>31</v>
+      </c>
+      <c r="K130">
+        <v>32</v>
+      </c>
+      <c r="L130">
+        <v>1.875</v>
+      </c>
+      <c r="N130">
+        <v>160</v>
+      </c>
+      <c r="O130" t="s">
+        <v>71</v>
+      </c>
+      <c r="P130">
+        <v>10</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>83</v>
+      </c>
+      <c r="R130">
+        <v>60</v>
+      </c>
+      <c r="S130">
+        <v>166.66666699999999</v>
+      </c>
+      <c r="X130">
+        <v>0</v>
+      </c>
+      <c r="Y130">
+        <v>0</v>
+      </c>
+      <c r="Z130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>38</v>
+      </c>
+      <c r="B131" t="s">
+        <v>37</v>
+      </c>
+      <c r="C131" t="s">
+        <v>82</v>
+      </c>
+      <c r="D131" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" t="s">
+        <v>40</v>
+      </c>
+      <c r="F131" t="s">
+        <v>33</v>
+      </c>
+      <c r="G131" t="s">
+        <v>32</v>
+      </c>
+      <c r="H131" t="s">
+        <v>31</v>
+      </c>
+      <c r="I131">
+        <v>39</v>
+      </c>
+      <c r="J131" t="s">
+        <v>30</v>
+      </c>
+      <c r="K131">
+        <v>730</v>
+      </c>
+      <c r="L131">
+        <v>1.435616</v>
+      </c>
+      <c r="M131">
+        <v>14.76923077</v>
+      </c>
+      <c r="N131">
+        <v>160</v>
+      </c>
+      <c r="O131" t="s">
+        <v>71</v>
+      </c>
+      <c r="P131">
+        <v>576</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>83</v>
+      </c>
+      <c r="R131">
+        <v>1048</v>
+      </c>
+      <c r="S131">
+        <v>549.61832100000004</v>
+      </c>
+      <c r="T131">
+        <v>39</v>
+      </c>
+      <c r="V131">
+        <v>14.769231</v>
+      </c>
+      <c r="W131">
+        <v>3.721374</v>
+      </c>
+      <c r="X131">
+        <v>47</v>
+      </c>
+      <c r="Y131">
+        <v>4.4847330000000003</v>
+      </c>
+      <c r="Z131">
+        <v>12.255319</v>
+      </c>
+    </row>
+    <row r="132" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>38</v>
+      </c>
+      <c r="B132" t="s">
+        <v>37</v>
+      </c>
+      <c r="C132" t="s">
+        <v>82</v>
+      </c>
+      <c r="D132" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" t="s">
+        <v>34</v>
+      </c>
+      <c r="F132" t="s">
+        <v>33</v>
+      </c>
+      <c r="G132" t="s">
+        <v>32</v>
+      </c>
+      <c r="H132" t="s">
+        <v>31</v>
+      </c>
+      <c r="I132">
+        <v>63</v>
+      </c>
+      <c r="J132" t="s">
+        <v>30</v>
+      </c>
+      <c r="K132">
+        <v>972</v>
+      </c>
+      <c r="L132">
+        <v>1.4495880000000001</v>
+      </c>
+      <c r="M132">
+        <v>17.428571430000002</v>
+      </c>
+      <c r="N132">
+        <v>160</v>
+      </c>
+      <c r="O132" t="s">
+        <v>71</v>
+      </c>
+      <c r="P132">
+        <v>1098</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>83</v>
+      </c>
+      <c r="R132">
+        <v>1409</v>
+      </c>
+      <c r="S132">
+        <v>779.27608199999997</v>
+      </c>
+      <c r="T132">
+        <v>63</v>
+      </c>
+      <c r="V132">
+        <v>17.428571000000002</v>
+      </c>
+      <c r="W132">
+        <v>4.4712560000000003</v>
+      </c>
+      <c r="X132">
+        <v>85</v>
+      </c>
+      <c r="Y132">
+        <v>6.0326469999999999</v>
+      </c>
+      <c r="Z132">
+        <v>12.917647000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>38</v>
+      </c>
+      <c r="B133" t="s">
+        <v>37</v>
+      </c>
+      <c r="C133" t="s">
+        <v>84</v>
+      </c>
+      <c r="D133" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" t="s">
+        <v>43</v>
+      </c>
+      <c r="F133" t="s">
+        <v>33</v>
+      </c>
+      <c r="G133" t="s">
+        <v>32</v>
+      </c>
+      <c r="H133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I133">
+        <v>57</v>
+      </c>
+      <c r="J133" t="s">
+        <v>30</v>
+      </c>
+      <c r="K133">
+        <v>1697</v>
+      </c>
+      <c r="L133">
+        <v>1.4119029999999999</v>
+      </c>
+      <c r="M133">
+        <v>59.315789469999999</v>
+      </c>
+      <c r="N133">
+        <v>160</v>
+      </c>
+      <c r="O133" t="s">
+        <v>71</v>
+      </c>
+      <c r="P133">
+        <v>3381</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>83</v>
+      </c>
+      <c r="R133">
+        <v>2396</v>
+      </c>
+      <c r="S133">
+        <v>1411.101836</v>
+      </c>
+      <c r="T133">
+        <v>57</v>
+      </c>
+      <c r="V133">
+        <v>59.315789000000002</v>
+      </c>
+      <c r="W133">
+        <v>2.378965</v>
+      </c>
+      <c r="X133">
+        <v>72</v>
+      </c>
+      <c r="Y133">
+        <v>3.0050080000000001</v>
+      </c>
+      <c r="Z133">
+        <v>46.958333000000003</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>38</v>
+      </c>
+      <c r="B134" t="s">
+        <v>37</v>
+      </c>
+      <c r="C134" t="s">
+        <v>84</v>
+      </c>
+      <c r="D134" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" t="s">
+        <v>42</v>
+      </c>
+      <c r="F134" t="s">
+        <v>33</v>
+      </c>
+      <c r="G134" t="s">
+        <v>32</v>
+      </c>
+      <c r="H134" t="s">
+        <v>31</v>
+      </c>
+      <c r="I134">
+        <v>4</v>
+      </c>
+      <c r="J134" t="s">
+        <v>30</v>
+      </c>
+      <c r="K134">
+        <v>397</v>
+      </c>
+      <c r="L134">
+        <v>1.15869</v>
+      </c>
+      <c r="M134">
+        <v>51.25</v>
+      </c>
+      <c r="N134">
+        <v>160</v>
+      </c>
+      <c r="O134" t="s">
+        <v>71</v>
+      </c>
+      <c r="P134">
+        <v>205</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>83</v>
+      </c>
+      <c r="R134">
+        <v>460</v>
+      </c>
+      <c r="S134">
+        <v>445.652174</v>
+      </c>
+      <c r="T134">
+        <v>4</v>
+      </c>
+      <c r="V134">
+        <v>51.25</v>
+      </c>
+      <c r="W134">
+        <v>0.86956500000000003</v>
+      </c>
+      <c r="X134">
+        <v>7</v>
+      </c>
+      <c r="Y134">
+        <v>1.521739</v>
+      </c>
+      <c r="Z134">
+        <v>29.285713999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>38</v>
+      </c>
+      <c r="B135" t="s">
+        <v>37</v>
+      </c>
+      <c r="C135" t="s">
+        <v>84</v>
+      </c>
+      <c r="D135" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" t="s">
+        <v>41</v>
+      </c>
+      <c r="F135" t="s">
+        <v>33</v>
+      </c>
+      <c r="G135" t="s">
+        <v>32</v>
+      </c>
+      <c r="H135" t="s">
+        <v>31</v>
+      </c>
+      <c r="K135">
+        <v>19</v>
+      </c>
+      <c r="L135">
+        <v>1.1052630000000001</v>
+      </c>
+      <c r="N135">
+        <v>160</v>
+      </c>
+      <c r="O135" t="s">
+        <v>71</v>
+      </c>
+      <c r="P135">
+        <v>5</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>83</v>
+      </c>
+      <c r="R135">
+        <v>21</v>
+      </c>
+      <c r="S135">
+        <v>238.09523799999999</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>0</v>
+      </c>
+      <c r="Z135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>38</v>
+      </c>
+      <c r="B136" t="s">
+        <v>37</v>
+      </c>
+      <c r="C136" t="s">
+        <v>84</v>
+      </c>
+      <c r="D136" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" t="s">
+        <v>40</v>
+      </c>
+      <c r="F136" t="s">
+        <v>33</v>
+      </c>
+      <c r="G136" t="s">
+        <v>32</v>
+      </c>
+      <c r="H136" t="s">
+        <v>31</v>
+      </c>
+      <c r="I136">
+        <v>2</v>
+      </c>
+      <c r="J136" t="s">
+        <v>30</v>
+      </c>
+      <c r="K136">
+        <v>165</v>
+      </c>
+      <c r="L136">
+        <v>1.206061</v>
+      </c>
+      <c r="M136">
+        <v>69</v>
+      </c>
+      <c r="N136">
+        <v>160</v>
+      </c>
+      <c r="O136" t="s">
+        <v>71</v>
+      </c>
+      <c r="P136">
+        <v>138</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>83</v>
+      </c>
+      <c r="R136">
+        <v>199</v>
+      </c>
+      <c r="S136">
+        <v>693.46733700000004</v>
+      </c>
+      <c r="T136">
+        <v>2</v>
+      </c>
+      <c r="V136">
+        <v>69</v>
+      </c>
+      <c r="W136">
+        <v>1.0050250000000001</v>
+      </c>
+      <c r="X136">
+        <v>4</v>
+      </c>
+      <c r="Y136">
+        <v>2.0100500000000001</v>
+      </c>
+      <c r="Z136">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>38</v>
+      </c>
+      <c r="B137" t="s">
+        <v>37</v>
+      </c>
+      <c r="C137" t="s">
+        <v>84</v>
+      </c>
+      <c r="D137" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" t="s">
+        <v>34</v>
+      </c>
+      <c r="F137" t="s">
+        <v>33</v>
+      </c>
+      <c r="G137" t="s">
+        <v>32</v>
+      </c>
+      <c r="H137" t="s">
+        <v>31</v>
+      </c>
+      <c r="I137">
+        <v>29</v>
+      </c>
+      <c r="J137" t="s">
+        <v>30</v>
+      </c>
+      <c r="K137">
+        <v>1101</v>
+      </c>
+      <c r="L137">
+        <v>1.380563</v>
+      </c>
+      <c r="M137">
+        <v>42.034482760000003</v>
+      </c>
+      <c r="N137">
+        <v>160</v>
+      </c>
+      <c r="O137" t="s">
+        <v>71</v>
+      </c>
+      <c r="P137">
+        <v>1219</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>83</v>
+      </c>
+      <c r="R137">
+        <v>1520</v>
+      </c>
+      <c r="S137">
+        <v>801.97368400000005</v>
+      </c>
+      <c r="T137">
+        <v>29</v>
+      </c>
+      <c r="V137">
+        <v>42.034483000000002</v>
+      </c>
+      <c r="W137">
+        <v>1.9078949999999999</v>
+      </c>
+      <c r="X137">
+        <v>40</v>
+      </c>
+      <c r="Y137">
+        <v>2.6315789999999999</v>
+      </c>
+      <c r="Z137">
+        <v>30.475000000000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>38</v>
+      </c>
+      <c r="B138" t="s">
+        <v>37</v>
+      </c>
+      <c r="C138" t="s">
+        <v>85</v>
+      </c>
+      <c r="D138" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" t="s">
+        <v>43</v>
+      </c>
+      <c r="F138" t="s">
+        <v>70</v>
+      </c>
+      <c r="G138" t="s">
+        <v>32</v>
+      </c>
+      <c r="H138" t="s">
+        <v>31</v>
+      </c>
+      <c r="K138">
+        <v>6</v>
+      </c>
+      <c r="L138">
+        <v>1.1666669999999999</v>
+      </c>
+      <c r="N138">
+        <v>160</v>
+      </c>
+      <c r="O138" t="s">
+        <v>71</v>
+      </c>
+      <c r="P138">
+        <v>3</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>83</v>
+      </c>
+      <c r="R138">
+        <v>7</v>
+      </c>
+      <c r="S138">
+        <v>428.57142900000002</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>38</v>
+      </c>
+      <c r="B139" t="s">
+        <v>37</v>
+      </c>
+      <c r="C139" t="s">
+        <v>85</v>
+      </c>
+      <c r="D139" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" t="s">
+        <v>43</v>
+      </c>
+      <c r="F139" t="s">
+        <v>33</v>
+      </c>
+      <c r="G139" t="s">
+        <v>32</v>
+      </c>
+      <c r="H139" t="s">
+        <v>31</v>
+      </c>
+      <c r="I139">
+        <v>85</v>
+      </c>
+      <c r="J139" t="s">
+        <v>30</v>
+      </c>
+      <c r="K139">
+        <v>1279</v>
+      </c>
+      <c r="L139">
+        <v>1.683346</v>
+      </c>
+      <c r="M139">
+        <v>12.95294118</v>
+      </c>
+      <c r="N139">
+        <v>160</v>
+      </c>
+      <c r="O139" t="s">
+        <v>71</v>
+      </c>
+      <c r="P139">
+        <v>1101</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>83</v>
+      </c>
+      <c r="R139">
+        <v>2153</v>
+      </c>
+      <c r="S139">
+        <v>511.37947100000002</v>
+      </c>
+      <c r="T139">
+        <v>85</v>
+      </c>
+      <c r="V139">
+        <v>12.952940999999999</v>
+      </c>
+      <c r="W139">
+        <v>3.9479799999999998</v>
+      </c>
+      <c r="X139">
+        <v>92</v>
+      </c>
+      <c r="Y139">
+        <v>4.2731070000000004</v>
+      </c>
+      <c r="Z139">
+        <v>11.967390999999999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>38</v>
+      </c>
+      <c r="B140" t="s">
+        <v>37</v>
+      </c>
+      <c r="C140" t="s">
+        <v>85</v>
+      </c>
+      <c r="D140" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" t="s">
+        <v>42</v>
+      </c>
+      <c r="F140" t="s">
+        <v>33</v>
+      </c>
+      <c r="G140" t="s">
+        <v>32</v>
+      </c>
+      <c r="H140" t="s">
+        <v>31</v>
+      </c>
+      <c r="I140">
+        <v>11</v>
+      </c>
+      <c r="J140" t="s">
+        <v>30</v>
+      </c>
+      <c r="K140">
+        <v>256</v>
+      </c>
+      <c r="L140">
+        <v>1.402344</v>
+      </c>
+      <c r="M140">
+        <v>12.727272729999999</v>
+      </c>
+      <c r="N140">
+        <v>160</v>
+      </c>
+      <c r="O140" t="s">
+        <v>71</v>
+      </c>
+      <c r="P140">
+        <v>140</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>83</v>
+      </c>
+      <c r="R140">
+        <v>359</v>
+      </c>
+      <c r="S140">
+        <v>389.97214500000001</v>
+      </c>
+      <c r="T140">
+        <v>11</v>
+      </c>
+      <c r="V140">
+        <v>12.727273</v>
+      </c>
+      <c r="W140">
+        <v>3.0640670000000001</v>
+      </c>
+      <c r="X140">
+        <v>13</v>
+      </c>
+      <c r="Y140">
+        <v>3.6211700000000002</v>
+      </c>
+      <c r="Z140">
+        <v>10.769231</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>38</v>
+      </c>
+      <c r="B141" t="s">
+        <v>37</v>
+      </c>
+      <c r="C141" t="s">
+        <v>85</v>
+      </c>
+      <c r="D141" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" t="s">
+        <v>41</v>
+      </c>
+      <c r="F141" t="s">
+        <v>33</v>
+      </c>
+      <c r="G141" t="s">
+        <v>32</v>
+      </c>
+      <c r="H141" t="s">
+        <v>31</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141" t="s">
+        <v>30</v>
+      </c>
+      <c r="K141">
+        <v>47</v>
+      </c>
+      <c r="L141">
+        <v>1.446809</v>
+      </c>
+      <c r="M141">
+        <v>7.5</v>
+      </c>
+      <c r="N141">
+        <v>160</v>
+      </c>
+      <c r="O141" t="s">
+        <v>71</v>
+      </c>
+      <c r="P141">
+        <v>15</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>83</v>
+      </c>
+      <c r="R141">
+        <v>68</v>
+      </c>
+      <c r="S141">
+        <v>220.588235</v>
+      </c>
+      <c r="T141">
+        <v>2</v>
+      </c>
+      <c r="V141">
+        <v>7.5</v>
+      </c>
+      <c r="W141">
+        <v>2.941176</v>
+      </c>
+      <c r="X141">
+        <v>3</v>
+      </c>
+      <c r="Y141">
+        <v>4.4117649999999999</v>
+      </c>
+      <c r="Z141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>38</v>
+      </c>
+      <c r="B142" t="s">
+        <v>37</v>
+      </c>
+      <c r="C142" t="s">
+        <v>85</v>
+      </c>
+      <c r="D142" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" t="s">
+        <v>40</v>
+      </c>
+      <c r="F142" t="s">
+        <v>33</v>
+      </c>
+      <c r="G142" t="s">
+        <v>32</v>
+      </c>
+      <c r="H142" t="s">
+        <v>31</v>
+      </c>
+      <c r="I142">
+        <v>50</v>
+      </c>
+      <c r="J142" t="s">
+        <v>30</v>
+      </c>
+      <c r="K142">
+        <v>867</v>
+      </c>
+      <c r="L142">
+        <v>1.3921570000000001</v>
+      </c>
+      <c r="M142">
+        <v>14.7</v>
+      </c>
+      <c r="N142">
+        <v>160</v>
+      </c>
+      <c r="O142" t="s">
+        <v>71</v>
+      </c>
+      <c r="P142">
+        <v>735</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>83</v>
+      </c>
+      <c r="R142">
+        <v>1207</v>
+      </c>
+      <c r="S142">
+        <v>608.94780400000002</v>
+      </c>
+      <c r="T142">
+        <v>50</v>
+      </c>
+      <c r="V142">
+        <v>14.7</v>
+      </c>
+      <c r="W142">
+        <v>4.1425020000000004</v>
+      </c>
+      <c r="X142">
+        <v>66</v>
+      </c>
+      <c r="Y142">
+        <v>5.4681030000000002</v>
+      </c>
+      <c r="Z142">
+        <v>11.136364</v>
+      </c>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>38</v>
+      </c>
+      <c r="B143" t="s">
+        <v>37</v>
+      </c>
+      <c r="C143" t="s">
+        <v>85</v>
+      </c>
+      <c r="D143" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" t="s">
+        <v>34</v>
+      </c>
+      <c r="F143" t="s">
+        <v>33</v>
+      </c>
+      <c r="G143" t="s">
+        <v>32</v>
+      </c>
+      <c r="H143" t="s">
+        <v>31</v>
+      </c>
+      <c r="I143">
+        <v>204</v>
+      </c>
+      <c r="J143" t="s">
+        <v>30</v>
+      </c>
+      <c r="K143">
+        <v>2338</v>
+      </c>
+      <c r="L143">
+        <v>1.762618</v>
+      </c>
+      <c r="M143">
+        <v>14.514705879999999</v>
+      </c>
+      <c r="N143">
+        <v>160</v>
+      </c>
+      <c r="O143" t="s">
+        <v>71</v>
+      </c>
+      <c r="P143">
+        <v>2961</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>83</v>
+      </c>
+      <c r="R143">
+        <v>4121</v>
+      </c>
+      <c r="S143">
+        <v>718.51492399999995</v>
+      </c>
+      <c r="T143">
+        <v>204</v>
+      </c>
+      <c r="V143">
+        <v>14.514706</v>
+      </c>
+      <c r="W143">
+        <v>4.9502550000000003</v>
+      </c>
+      <c r="X143">
+        <v>253</v>
+      </c>
+      <c r="Y143">
+        <v>6.1392870000000004</v>
+      </c>
+      <c r="Z143">
+        <v>11.703557</v>
+      </c>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>38</v>
+      </c>
+      <c r="B144" t="s">
+        <v>37</v>
+      </c>
+      <c r="C144" t="s">
+        <v>86</v>
+      </c>
+      <c r="D144" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" t="s">
+        <v>43</v>
+      </c>
+      <c r="F144" t="s">
+        <v>33</v>
+      </c>
+      <c r="G144" t="s">
+        <v>32</v>
+      </c>
+      <c r="H144" t="s">
+        <v>31</v>
+      </c>
+      <c r="I144">
+        <v>115</v>
+      </c>
+      <c r="J144" t="s">
+        <v>30</v>
+      </c>
+      <c r="K144">
+        <v>1968</v>
+      </c>
+      <c r="L144">
+        <v>1.5345530000000001</v>
+      </c>
+      <c r="M144">
+        <v>11.339130430000001</v>
+      </c>
+      <c r="N144" t="s">
+        <v>29</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>1304</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>87</v>
+      </c>
+      <c r="R144">
+        <v>3020</v>
+      </c>
+      <c r="S144">
+        <v>431.78807899999998</v>
+      </c>
+      <c r="T144">
+        <v>115</v>
+      </c>
+      <c r="V144">
+        <v>11.339130000000001</v>
+      </c>
+      <c r="W144">
+        <v>3.807947</v>
+      </c>
+      <c r="X144">
+        <v>118</v>
+      </c>
+      <c r="Y144">
+        <v>3.9072849999999999</v>
+      </c>
+      <c r="Z144">
+        <v>11.050846999999999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>38</v>
+      </c>
+      <c r="B145" t="s">
+        <v>37</v>
+      </c>
+      <c r="C145" t="s">
+        <v>86</v>
+      </c>
+      <c r="D145" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" t="s">
+        <v>43</v>
+      </c>
+      <c r="F145" t="s">
+        <v>46</v>
+      </c>
+      <c r="G145" t="s">
+        <v>32</v>
+      </c>
+      <c r="H145" t="s">
+        <v>31</v>
+      </c>
+      <c r="K145">
+        <v>2</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="N145" t="s">
+        <v>29</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>2</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>87</v>
+      </c>
+      <c r="R145">
+        <v>2</v>
+      </c>
+      <c r="S145">
+        <v>1000</v>
+      </c>
+      <c r="X145">
+        <v>0</v>
+      </c>
+      <c r="Y145">
+        <v>0</v>
+      </c>
+      <c r="Z145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>38</v>
+      </c>
+      <c r="B146" t="s">
+        <v>37</v>
+      </c>
+      <c r="C146" t="s">
+        <v>86</v>
+      </c>
+      <c r="D146" t="s">
+        <v>35</v>
+      </c>
+      <c r="E146" t="s">
+        <v>42</v>
+      </c>
+      <c r="F146" t="s">
+        <v>33</v>
+      </c>
+      <c r="G146" t="s">
+        <v>32</v>
+      </c>
+      <c r="H146" t="s">
+        <v>31</v>
+      </c>
+      <c r="I146">
+        <v>15</v>
+      </c>
+      <c r="J146" t="s">
+        <v>30</v>
+      </c>
+      <c r="K146">
+        <v>490</v>
+      </c>
+      <c r="L146">
+        <v>1.4020410000000001</v>
+      </c>
+      <c r="M146">
+        <v>12.93333333</v>
+      </c>
+      <c r="N146" t="s">
+        <v>29</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>194</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>87</v>
+      </c>
+      <c r="R146">
+        <v>687</v>
+      </c>
+      <c r="S146">
+        <v>282.38719099999997</v>
+      </c>
+      <c r="T146">
+        <v>15</v>
+      </c>
+      <c r="V146">
+        <v>12.933332999999999</v>
+      </c>
+      <c r="W146">
+        <v>2.1834060000000002</v>
+      </c>
+      <c r="X146">
+        <v>15</v>
+      </c>
+      <c r="Y146">
+        <v>2.1834060000000002</v>
+      </c>
+      <c r="Z146">
+        <v>12.933332999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>38</v>
+      </c>
+      <c r="B147" t="s">
+        <v>37</v>
+      </c>
+      <c r="C147" t="s">
+        <v>86</v>
+      </c>
+      <c r="D147" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" t="s">
+        <v>41</v>
+      </c>
+      <c r="F147" t="s">
+        <v>33</v>
+      </c>
+      <c r="G147" t="s">
+        <v>32</v>
+      </c>
+      <c r="H147" t="s">
+        <v>31</v>
+      </c>
+      <c r="I147">
+        <v>3</v>
+      </c>
+      <c r="J147" t="s">
+        <v>30</v>
+      </c>
+      <c r="K147">
+        <v>88</v>
+      </c>
+      <c r="L147">
+        <v>1.295455</v>
+      </c>
+      <c r="M147">
+        <v>6</v>
+      </c>
+      <c r="N147" t="s">
+        <v>29</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>18</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>87</v>
+      </c>
+      <c r="R147">
+        <v>114</v>
+      </c>
+      <c r="S147">
+        <v>157.89473699999999</v>
+      </c>
+      <c r="T147">
+        <v>3</v>
+      </c>
+      <c r="V147">
+        <v>6</v>
+      </c>
+      <c r="W147">
+        <v>2.6315789999999999</v>
+      </c>
+      <c r="X147">
+        <v>3</v>
+      </c>
+      <c r="Y147">
+        <v>2.6315789999999999</v>
+      </c>
+      <c r="Z147">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>38</v>
+      </c>
+      <c r="B148" t="s">
+        <v>37</v>
+      </c>
+      <c r="C148" t="s">
+        <v>86</v>
+      </c>
+      <c r="D148" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" t="s">
+        <v>40</v>
+      </c>
+      <c r="F148" t="s">
+        <v>33</v>
+      </c>
+      <c r="G148" t="s">
+        <v>32</v>
+      </c>
+      <c r="H148" t="s">
+        <v>31</v>
+      </c>
+      <c r="I148">
+        <v>133</v>
+      </c>
+      <c r="J148" t="s">
+        <v>30</v>
+      </c>
+      <c r="K148">
+        <v>2244</v>
+      </c>
+      <c r="L148">
+        <v>1.4469700000000001</v>
+      </c>
+      <c r="M148">
+        <v>11.54887218</v>
+      </c>
+      <c r="N148" t="s">
+        <v>29</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>1536</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>87</v>
+      </c>
+      <c r="R148">
+        <v>3247</v>
+      </c>
+      <c r="S148">
+        <v>473.05204800000001</v>
+      </c>
+      <c r="T148">
+        <v>133</v>
+      </c>
+      <c r="V148">
+        <v>11.548871999999999</v>
+      </c>
+      <c r="W148">
+        <v>4.0960890000000001</v>
+      </c>
+      <c r="X148">
+        <v>170</v>
+      </c>
+      <c r="Y148">
+        <v>5.2356020000000001</v>
+      </c>
+      <c r="Z148">
+        <v>9.0352940000000004</v>
+      </c>
+    </row>
+    <row r="149" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>38</v>
+      </c>
+      <c r="B149" t="s">
+        <v>37</v>
+      </c>
+      <c r="C149" t="s">
+        <v>86</v>
+      </c>
+      <c r="D149" t="s">
+        <v>35</v>
+      </c>
+      <c r="E149" t="s">
+        <v>34</v>
+      </c>
+      <c r="F149" t="s">
+        <v>33</v>
+      </c>
+      <c r="G149" t="s">
+        <v>32</v>
+      </c>
+      <c r="H149" t="s">
+        <v>31</v>
+      </c>
+      <c r="I149">
+        <v>205</v>
+      </c>
+      <c r="J149" t="s">
+        <v>30</v>
+      </c>
+      <c r="K149">
+        <v>2650</v>
+      </c>
+      <c r="L149">
+        <v>1.603774</v>
+      </c>
+      <c r="M149">
+        <v>12.975609759999999</v>
+      </c>
+      <c r="N149" t="s">
+        <v>29</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>2660</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>87</v>
+      </c>
+      <c r="R149">
+        <v>4250</v>
+      </c>
+      <c r="S149">
+        <v>625.88235299999997</v>
+      </c>
+      <c r="T149">
+        <v>205</v>
+      </c>
+      <c r="V149">
+        <v>12.97561</v>
+      </c>
+      <c r="W149">
+        <v>4.8235289999999997</v>
+      </c>
+      <c r="X149">
+        <v>248</v>
+      </c>
+      <c r="Y149">
+        <v>5.8352940000000002</v>
+      </c>
+      <c r="Z149">
+        <v>10.725806</v>
+      </c>
+    </row>
+    <row r="150" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>38</v>
+      </c>
+      <c r="B150" t="s">
+        <v>37</v>
+      </c>
+      <c r="C150" t="s">
+        <v>86</v>
+      </c>
+      <c r="D150" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" t="s">
+        <v>34</v>
+      </c>
+      <c r="F150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G150" t="s">
+        <v>32</v>
+      </c>
+      <c r="H150" t="s">
+        <v>31</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="N150" t="s">
+        <v>29</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>1</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>87</v>
+      </c>
+      <c r="R150">
+        <v>1</v>
+      </c>
+      <c r="S150">
+        <v>1000</v>
+      </c>
+      <c r="X150">
+        <v>0</v>
+      </c>
+      <c r="Y150">
+        <v>0</v>
+      </c>
+      <c r="Z150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>38</v>
+      </c>
+      <c r="B151" t="s">
+        <v>37</v>
+      </c>
+      <c r="C151" t="s">
+        <v>88</v>
+      </c>
+      <c r="D151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" t="s">
+        <v>43</v>
+      </c>
+      <c r="F151" t="s">
+        <v>33</v>
+      </c>
+      <c r="G151" t="s">
+        <v>32</v>
+      </c>
+      <c r="H151" t="s">
+        <v>31</v>
+      </c>
+      <c r="I151">
+        <v>333</v>
+      </c>
+      <c r="J151" t="s">
+        <v>30</v>
+      </c>
+      <c r="K151">
+        <v>6116</v>
+      </c>
+      <c r="L151">
+        <v>1.5142249999999999</v>
+      </c>
+      <c r="M151">
+        <v>10.85585586</v>
+      </c>
+      <c r="N151" t="s">
+        <v>29</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>3615</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>87</v>
+      </c>
+      <c r="R151">
+        <v>9261</v>
+      </c>
+      <c r="S151">
+        <v>390.34661499999999</v>
+      </c>
+      <c r="T151">
+        <v>333</v>
+      </c>
+      <c r="V151">
+        <v>10.855855999999999</v>
+      </c>
+      <c r="W151">
+        <v>3.5957240000000001</v>
+      </c>
+      <c r="X151">
+        <v>349</v>
+      </c>
+      <c r="Y151">
+        <v>3.7684920000000002</v>
+      </c>
+      <c r="Z151">
+        <v>10.358166000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>38</v>
+      </c>
+      <c r="B152" t="s">
+        <v>37</v>
+      </c>
+      <c r="C152" t="s">
+        <v>88</v>
+      </c>
+      <c r="D152" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" t="s">
+        <v>43</v>
+      </c>
+      <c r="F152" t="s">
+        <v>46</v>
+      </c>
+      <c r="G152" t="s">
+        <v>32</v>
+      </c>
+      <c r="H152" t="s">
+        <v>31</v>
+      </c>
+      <c r="K152">
+        <v>6</v>
+      </c>
+      <c r="L152">
+        <v>1.5</v>
+      </c>
+      <c r="N152" t="s">
+        <v>29</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>1</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>87</v>
+      </c>
+      <c r="R152">
+        <v>9</v>
+      </c>
+      <c r="S152">
+        <v>111.11111099999999</v>
+      </c>
+      <c r="X152">
+        <v>0</v>
+      </c>
+      <c r="Y152">
+        <v>0</v>
+      </c>
+      <c r="Z152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>38</v>
+      </c>
+      <c r="B153" t="s">
+        <v>37</v>
+      </c>
+      <c r="C153" t="s">
+        <v>88</v>
+      </c>
+      <c r="D153" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" t="s">
+        <v>42</v>
+      </c>
+      <c r="F153" t="s">
+        <v>33</v>
+      </c>
+      <c r="G153" t="s">
+        <v>32</v>
+      </c>
+      <c r="H153" t="s">
+        <v>31</v>
+      </c>
+      <c r="I153">
+        <v>25</v>
+      </c>
+      <c r="J153" t="s">
+        <v>30</v>
+      </c>
+      <c r="K153">
+        <v>732</v>
+      </c>
+      <c r="L153">
+        <v>1.4180330000000001</v>
+      </c>
+      <c r="M153">
+        <v>10.64</v>
+      </c>
+      <c r="N153" t="s">
+        <v>29</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>266</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>87</v>
+      </c>
+      <c r="R153">
+        <v>1038</v>
+      </c>
+      <c r="S153">
+        <v>256.26204200000001</v>
+      </c>
+      <c r="T153">
+        <v>25</v>
+      </c>
+      <c r="V153">
+        <v>10.64</v>
+      </c>
+      <c r="W153">
+        <v>2.4084780000000001</v>
+      </c>
+      <c r="X153">
+        <v>26</v>
+      </c>
+      <c r="Y153">
+        <v>2.5048170000000001</v>
+      </c>
+      <c r="Z153">
+        <v>10.230769</v>
+      </c>
+    </row>
+    <row r="154" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>38</v>
+      </c>
+      <c r="B154" t="s">
+        <v>37</v>
+      </c>
+      <c r="C154" t="s">
+        <v>88</v>
+      </c>
+      <c r="D154" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" t="s">
+        <v>41</v>
+      </c>
+      <c r="F154" t="s">
+        <v>33</v>
+      </c>
+      <c r="G154" t="s">
+        <v>32</v>
+      </c>
+      <c r="H154" t="s">
+        <v>31</v>
+      </c>
+      <c r="K154">
+        <v>94</v>
+      </c>
+      <c r="L154">
+        <v>1.0425530000000001</v>
+      </c>
+      <c r="N154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>9</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>87</v>
+      </c>
+      <c r="R154">
+        <v>98</v>
+      </c>
+      <c r="S154">
+        <v>91.836735000000004</v>
+      </c>
+      <c r="X154">
+        <v>0</v>
+      </c>
+      <c r="Y154">
+        <v>0</v>
+      </c>
+      <c r="Z154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>38</v>
+      </c>
+      <c r="B155" t="s">
+        <v>37</v>
+      </c>
+      <c r="C155" t="s">
+        <v>88</v>
+      </c>
+      <c r="D155" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" t="s">
+        <v>40</v>
+      </c>
+      <c r="F155" t="s">
+        <v>33</v>
+      </c>
+      <c r="G155" t="s">
+        <v>32</v>
+      </c>
+      <c r="H155" t="s">
+        <v>31</v>
+      </c>
+      <c r="I155">
+        <v>134</v>
+      </c>
+      <c r="J155" t="s">
+        <v>30</v>
+      </c>
+      <c r="K155">
+        <v>2028</v>
+      </c>
+      <c r="L155">
+        <v>1.294872</v>
+      </c>
+      <c r="M155">
+        <v>8.4850746299999997</v>
+      </c>
+      <c r="N155" t="s">
+        <v>29</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>1137</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>87</v>
+      </c>
+      <c r="R155">
+        <v>2626</v>
+      </c>
+      <c r="S155">
+        <v>432.977913</v>
+      </c>
+      <c r="T155">
+        <v>134</v>
+      </c>
+      <c r="V155">
+        <v>8.4850750000000001</v>
+      </c>
+      <c r="W155">
+        <v>5.1028180000000001</v>
+      </c>
+      <c r="X155">
+        <v>153</v>
+      </c>
+      <c r="Y155">
+        <v>5.826352</v>
+      </c>
+      <c r="Z155">
+        <v>7.4313729999999998</v>
+      </c>
+    </row>
+    <row r="156" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>38</v>
+      </c>
+      <c r="B156" t="s">
+        <v>37</v>
+      </c>
+      <c r="C156" t="s">
+        <v>88</v>
+      </c>
+      <c r="D156" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" t="s">
+        <v>34</v>
+      </c>
+      <c r="F156" t="s">
+        <v>33</v>
+      </c>
+      <c r="G156" t="s">
+        <v>32</v>
+      </c>
+      <c r="H156" t="s">
+        <v>31</v>
+      </c>
+      <c r="I156">
+        <v>45</v>
+      </c>
+      <c r="J156" t="s">
+        <v>30</v>
+      </c>
+      <c r="K156">
+        <v>644</v>
+      </c>
+      <c r="L156">
+        <v>1.363354</v>
+      </c>
+      <c r="M156">
+        <v>11.55555556</v>
+      </c>
+      <c r="N156" t="s">
+        <v>29</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>520</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>87</v>
+      </c>
+      <c r="R156">
+        <v>878</v>
+      </c>
+      <c r="S156">
+        <v>592.25512500000002</v>
+      </c>
+      <c r="T156">
+        <v>45</v>
+      </c>
+      <c r="V156">
+        <v>11.555555999999999</v>
+      </c>
+      <c r="W156">
+        <v>5.1252849999999999</v>
+      </c>
+      <c r="X156">
+        <v>46</v>
+      </c>
+      <c r="Y156">
+        <v>5.2391800000000002</v>
+      </c>
+      <c r="Z156">
+        <v>11.304347999999999</v>
+      </c>
+    </row>
+    <row r="157" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>38</v>
+      </c>
+      <c r="B157" t="s">
+        <v>37</v>
+      </c>
+      <c r="C157" t="s">
+        <v>88</v>
+      </c>
+      <c r="D157" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" t="s">
+        <v>34</v>
+      </c>
+      <c r="F157" t="s">
+        <v>46</v>
+      </c>
+      <c r="G157" t="s">
+        <v>32</v>
+      </c>
+      <c r="H157" t="s">
+        <v>31</v>
+      </c>
+      <c r="K157">
+        <v>6</v>
+      </c>
+      <c r="L157">
+        <v>1</v>
+      </c>
+      <c r="N157" t="s">
+        <v>29</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>4</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>87</v>
+      </c>
+      <c r="R157">
+        <v>6</v>
+      </c>
+      <c r="S157">
+        <v>666.66666699999996</v>
+      </c>
+      <c r="X157">
+        <v>0</v>
+      </c>
+      <c r="Y157">
+        <v>0</v>
+      </c>
+      <c r="Z157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>38</v>
+      </c>
+      <c r="B158" t="s">
+        <v>37</v>
+      </c>
+      <c r="C158" t="s">
+        <v>89</v>
+      </c>
+      <c r="D158" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" t="s">
+        <v>43</v>
+      </c>
+      <c r="F158" t="s">
+        <v>33</v>
+      </c>
+      <c r="G158" t="s">
+        <v>32</v>
+      </c>
+      <c r="H158" t="s">
+        <v>31</v>
+      </c>
+      <c r="I158">
+        <v>68</v>
+      </c>
+      <c r="J158" t="s">
+        <v>30</v>
+      </c>
+      <c r="K158">
+        <v>2366</v>
+      </c>
+      <c r="L158">
+        <v>1.681319</v>
+      </c>
+      <c r="M158">
+        <v>37.352941180000002</v>
+      </c>
+      <c r="N158" t="s">
+        <v>29</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>2540</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>67</v>
+      </c>
+      <c r="R158">
+        <v>3978</v>
+      </c>
+      <c r="S158">
+        <v>638.51181499999996</v>
+      </c>
+      <c r="T158">
+        <v>68</v>
+      </c>
+      <c r="V158">
+        <v>37.352941000000001</v>
+      </c>
+      <c r="W158">
+        <v>1.7094020000000001</v>
+      </c>
+      <c r="X158">
+        <v>118</v>
+      </c>
+      <c r="Y158">
+        <v>2.9663149999999998</v>
+      </c>
+      <c r="Z158">
+        <v>21.525424000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>38</v>
+      </c>
+      <c r="B159" t="s">
+        <v>37</v>
+      </c>
+      <c r="C159" t="s">
+        <v>89</v>
+      </c>
+      <c r="D159" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" t="s">
+        <v>42</v>
+      </c>
+      <c r="F159" t="s">
+        <v>33</v>
+      </c>
+      <c r="G159" t="s">
+        <v>32</v>
+      </c>
+      <c r="H159" t="s">
+        <v>31</v>
+      </c>
+      <c r="I159">
+        <v>5</v>
+      </c>
+      <c r="J159" t="s">
+        <v>30</v>
+      </c>
+      <c r="K159">
+        <v>372</v>
+      </c>
+      <c r="L159">
+        <v>1.424731</v>
+      </c>
+      <c r="M159">
+        <v>47</v>
+      </c>
+      <c r="N159" t="s">
+        <v>29</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <v>235</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>67</v>
+      </c>
+      <c r="R159">
+        <v>530</v>
+      </c>
+      <c r="S159">
+        <v>443.39622600000001</v>
+      </c>
+      <c r="T159">
+        <v>5</v>
+      </c>
+      <c r="V159">
+        <v>47</v>
+      </c>
+      <c r="W159">
+        <v>0.94339600000000001</v>
+      </c>
+      <c r="X159">
+        <v>7</v>
+      </c>
+      <c r="Y159">
+        <v>1.3207549999999999</v>
+      </c>
+      <c r="Z159">
+        <v>33.571429000000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>38</v>
+      </c>
+      <c r="B160" t="s">
+        <v>37</v>
+      </c>
+      <c r="C160" t="s">
+        <v>89</v>
+      </c>
+      <c r="D160" t="s">
+        <v>35</v>
+      </c>
+      <c r="E160" t="s">
+        <v>41</v>
+      </c>
+      <c r="F160" t="s">
+        <v>33</v>
+      </c>
+      <c r="G160" t="s">
+        <v>32</v>
+      </c>
+      <c r="H160" t="s">
+        <v>31</v>
+      </c>
+      <c r="K160">
+        <v>42</v>
+      </c>
+      <c r="L160">
+        <v>1.1666669999999999</v>
+      </c>
+      <c r="N160" t="s">
+        <v>29</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <v>11</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>67</v>
+      </c>
+      <c r="R160">
+        <v>49</v>
+      </c>
+      <c r="S160">
+        <v>224.48979600000001</v>
+      </c>
+      <c r="X160">
+        <v>0</v>
+      </c>
+      <c r="Y160">
+        <v>0</v>
+      </c>
+      <c r="Z160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>38</v>
+      </c>
+      <c r="B161" t="s">
+        <v>37</v>
+      </c>
+      <c r="C161" t="s">
+        <v>89</v>
+      </c>
+      <c r="D161" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" t="s">
+        <v>40</v>
+      </c>
+      <c r="F161" t="s">
+        <v>33</v>
+      </c>
+      <c r="G161" t="s">
+        <v>32</v>
+      </c>
+      <c r="H161" t="s">
+        <v>31</v>
+      </c>
+      <c r="I161">
+        <v>67</v>
+      </c>
+      <c r="J161" t="s">
+        <v>30</v>
+      </c>
+      <c r="K161">
+        <v>2762</v>
+      </c>
+      <c r="L161">
+        <v>1.39428</v>
+      </c>
+      <c r="M161">
+        <v>33.358208959999999</v>
+      </c>
+      <c r="N161" t="s">
+        <v>29</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <v>2235</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>67</v>
+      </c>
+      <c r="R161">
+        <v>3851</v>
+      </c>
+      <c r="S161">
+        <v>580.36873500000002</v>
+      </c>
+      <c r="T161">
+        <v>67</v>
+      </c>
+      <c r="V161">
+        <v>33.358209000000002</v>
+      </c>
+      <c r="W161">
+        <v>1.739808</v>
+      </c>
+      <c r="X161">
+        <v>121</v>
+      </c>
+      <c r="Y161">
+        <v>3.1420409999999999</v>
+      </c>
+      <c r="Z161">
+        <v>18.471074000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>38</v>
+      </c>
+      <c r="B162" t="s">
+        <v>37</v>
+      </c>
+      <c r="C162" t="s">
+        <v>89</v>
+      </c>
+      <c r="D162" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" t="s">
+        <v>34</v>
+      </c>
+      <c r="F162" t="s">
+        <v>33</v>
+      </c>
+      <c r="G162" t="s">
+        <v>32</v>
+      </c>
+      <c r="H162" t="s">
+        <v>31</v>
+      </c>
+      <c r="I162">
+        <v>30</v>
+      </c>
+      <c r="J162" t="s">
+        <v>30</v>
+      </c>
+      <c r="K162">
+        <v>778</v>
+      </c>
+      <c r="L162">
+        <v>1.4781489999999999</v>
+      </c>
+      <c r="M162">
+        <v>31.666666670000001</v>
+      </c>
+      <c r="N162" t="s">
+        <v>29</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>950</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>67</v>
+      </c>
+      <c r="R162">
+        <v>1150</v>
+      </c>
+      <c r="S162">
+        <v>826.08695699999998</v>
+      </c>
+      <c r="T162">
+        <v>30</v>
+      </c>
+      <c r="V162">
+        <v>31.666667</v>
+      </c>
+      <c r="W162">
+        <v>2.6086960000000001</v>
+      </c>
+      <c r="X162">
+        <v>37</v>
+      </c>
+      <c r="Y162">
+        <v>3.2173910000000001</v>
+      </c>
+      <c r="Z162">
+        <v>25.675675999999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>38</v>
+      </c>
+      <c r="B163" t="s">
+        <v>37</v>
+      </c>
+      <c r="C163" t="s">
+        <v>90</v>
+      </c>
+      <c r="D163" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" t="s">
+        <v>43</v>
+      </c>
+      <c r="F163" t="s">
+        <v>33</v>
+      </c>
+      <c r="G163" t="s">
+        <v>32</v>
+      </c>
+      <c r="H163" t="s">
+        <v>31</v>
+      </c>
+      <c r="I163">
+        <v>45</v>
+      </c>
+      <c r="J163" t="s">
+        <v>30</v>
+      </c>
+      <c r="K163">
+        <v>1085</v>
+      </c>
+      <c r="L163">
+        <v>1.623963</v>
+      </c>
+      <c r="M163">
+        <v>26.266666669999999</v>
+      </c>
+      <c r="N163" t="s">
+        <v>29</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>1182</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>87</v>
+      </c>
+      <c r="R163">
+        <v>1762</v>
+      </c>
+      <c r="S163">
+        <v>670.82860400000004</v>
+      </c>
+      <c r="T163">
+        <v>45</v>
+      </c>
+      <c r="V163">
+        <v>26.266667000000002</v>
+      </c>
+      <c r="W163">
+        <v>2.5539160000000001</v>
+      </c>
+      <c r="X163">
+        <v>48</v>
+      </c>
+      <c r="Y163">
+        <v>2.7241770000000001</v>
+      </c>
+      <c r="Z163">
+        <v>24.625</v>
+      </c>
+    </row>
+    <row r="164" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>38</v>
+      </c>
+      <c r="B164" t="s">
+        <v>37</v>
+      </c>
+      <c r="C164" t="s">
+        <v>90</v>
+      </c>
+      <c r="D164" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" t="s">
+        <v>43</v>
+      </c>
+      <c r="F164" t="s">
+        <v>46</v>
+      </c>
+      <c r="G164" t="s">
+        <v>32</v>
+      </c>
+      <c r="H164" t="s">
+        <v>31</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="N164" t="s">
+        <v>29</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>1</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>87</v>
+      </c>
+      <c r="R164">
+        <v>1</v>
+      </c>
+      <c r="S164">
+        <v>1000</v>
+      </c>
+      <c r="X164">
+        <v>0</v>
+      </c>
+      <c r="Y164">
+        <v>0</v>
+      </c>
+      <c r="Z164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>38</v>
+      </c>
+      <c r="B165" t="s">
+        <v>37</v>
+      </c>
+      <c r="C165" t="s">
+        <v>90</v>
+      </c>
+      <c r="D165" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" t="s">
+        <v>42</v>
+      </c>
+      <c r="F165" t="s">
+        <v>33</v>
+      </c>
+      <c r="G165" t="s">
+        <v>32</v>
+      </c>
+      <c r="H165" t="s">
+        <v>31</v>
+      </c>
+      <c r="I165">
+        <v>3</v>
+      </c>
+      <c r="J165" t="s">
+        <v>30</v>
+      </c>
+      <c r="K165">
+        <v>256</v>
+      </c>
+      <c r="L165">
+        <v>1.339844</v>
+      </c>
+      <c r="M165">
+        <v>43.666666669999998</v>
+      </c>
+      <c r="N165" t="s">
+        <v>29</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>131</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>87</v>
+      </c>
+      <c r="R165">
+        <v>343</v>
+      </c>
+      <c r="S165">
+        <v>381.92419799999999</v>
+      </c>
+      <c r="T165">
+        <v>3</v>
+      </c>
+      <c r="V165">
+        <v>43.666666999999997</v>
+      </c>
+      <c r="W165">
+        <v>0.87463599999999997</v>
+      </c>
+      <c r="X165">
+        <v>3</v>
+      </c>
+      <c r="Y165">
+        <v>0.87463599999999997</v>
+      </c>
+      <c r="Z165">
+        <v>43.666666999999997</v>
+      </c>
+    </row>
+    <row r="166" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>38</v>
+      </c>
+      <c r="B166" t="s">
+        <v>37</v>
+      </c>
+      <c r="C166" t="s">
+        <v>90</v>
+      </c>
+      <c r="D166" t="s">
+        <v>35</v>
+      </c>
+      <c r="E166" t="s">
+        <v>40</v>
+      </c>
+      <c r="F166" t="s">
+        <v>33</v>
+      </c>
+      <c r="G166" t="s">
+        <v>32</v>
+      </c>
+      <c r="H166" t="s">
+        <v>31</v>
+      </c>
+      <c r="I166">
+        <v>61</v>
+      </c>
+      <c r="J166" t="s">
+        <v>30</v>
+      </c>
+      <c r="K166">
+        <v>1364</v>
+      </c>
+      <c r="L166">
+        <v>1.5777129999999999</v>
+      </c>
+      <c r="M166">
+        <v>27.31147541</v>
+      </c>
+      <c r="N166" t="s">
+        <v>29</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>1666</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>87</v>
+      </c>
+      <c r="R166">
+        <v>2152</v>
+      </c>
+      <c r="S166">
+        <v>774.16356900000005</v>
+      </c>
+      <c r="T166">
+        <v>61</v>
+      </c>
+      <c r="V166">
+        <v>27.311475000000002</v>
+      </c>
+      <c r="W166">
+        <v>2.8345720000000001</v>
+      </c>
+      <c r="X166">
+        <v>84</v>
+      </c>
+      <c r="Y166">
+        <v>3.903346</v>
+      </c>
+      <c r="Z166">
+        <v>19.833333</v>
+      </c>
+    </row>
+    <row r="167" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>38</v>
+      </c>
+      <c r="B167" t="s">
+        <v>37</v>
+      </c>
+      <c r="C167" t="s">
+        <v>90</v>
+      </c>
+      <c r="D167" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" t="s">
+        <v>34</v>
+      </c>
+      <c r="F167" t="s">
+        <v>33</v>
+      </c>
+      <c r="G167" t="s">
+        <v>32</v>
+      </c>
+      <c r="H167" t="s">
+        <v>31</v>
+      </c>
+      <c r="I167">
+        <v>91</v>
+      </c>
+      <c r="J167" t="s">
+        <v>30</v>
+      </c>
+      <c r="K167">
+        <v>1695</v>
+      </c>
+      <c r="L167">
+        <v>1.6141589999999999</v>
+      </c>
+      <c r="M167">
+        <v>33.835164839999997</v>
+      </c>
+      <c r="N167" t="s">
+        <v>29</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>3079</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>87</v>
+      </c>
+      <c r="R167">
+        <v>2736</v>
+      </c>
+      <c r="S167">
+        <v>1125.365497</v>
+      </c>
+      <c r="T167">
+        <v>91</v>
+      </c>
+      <c r="V167">
+        <v>33.835165000000003</v>
+      </c>
+      <c r="W167">
+        <v>3.3260230000000002</v>
+      </c>
+      <c r="X167">
+        <v>111</v>
+      </c>
+      <c r="Y167">
+        <v>4.0570180000000002</v>
+      </c>
+      <c r="Z167">
+        <v>27.738738999999999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>38</v>
+      </c>
+      <c r="B168" t="s">
+        <v>37</v>
+      </c>
+      <c r="C168" t="s">
+        <v>91</v>
+      </c>
+      <c r="D168" t="s">
+        <v>35</v>
+      </c>
+      <c r="E168" t="s">
+        <v>43</v>
+      </c>
+      <c r="F168" t="s">
+        <v>33</v>
+      </c>
+      <c r="G168" t="s">
+        <v>32</v>
+      </c>
+      <c r="H168" t="s">
+        <v>31</v>
+      </c>
+      <c r="I168">
+        <v>66</v>
+      </c>
+      <c r="J168" t="s">
+        <v>30</v>
+      </c>
+      <c r="K168">
+        <v>768</v>
+      </c>
+      <c r="L168">
+        <v>1.535156</v>
+      </c>
+      <c r="M168">
+        <v>8.6363636400000008</v>
+      </c>
+      <c r="N168" t="s">
+        <v>29</v>
+      </c>
+      <c r="O168">
+        <v>0</v>
+      </c>
+      <c r="P168">
+        <v>570</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>67</v>
+      </c>
+      <c r="R168">
+        <v>1179</v>
+      </c>
+      <c r="S168">
+        <v>483.46055999999999</v>
+      </c>
+      <c r="T168">
+        <v>66</v>
+      </c>
+      <c r="V168">
+        <v>8.6363640000000004</v>
+      </c>
+      <c r="W168">
+        <v>5.5979640000000002</v>
+      </c>
+      <c r="X168">
+        <v>69</v>
+      </c>
+      <c r="Y168">
+        <v>5.852417</v>
+      </c>
+      <c r="Z168">
+        <v>8.2608700000000006</v>
+      </c>
+    </row>
+    <row r="169" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>38</v>
+      </c>
+      <c r="B169" t="s">
+        <v>37</v>
+      </c>
+      <c r="C169" t="s">
+        <v>91</v>
+      </c>
+      <c r="D169" t="s">
+        <v>35</v>
+      </c>
+      <c r="E169" t="s">
+        <v>42</v>
+      </c>
+      <c r="F169" t="s">
+        <v>33</v>
+      </c>
+      <c r="G169" t="s">
+        <v>32</v>
+      </c>
+      <c r="H169" t="s">
+        <v>31</v>
+      </c>
+      <c r="I169">
+        <v>3</v>
+      </c>
+      <c r="J169" t="s">
+        <v>30</v>
+      </c>
+      <c r="K169">
+        <v>56</v>
+      </c>
+      <c r="L169">
+        <v>1.035714</v>
+      </c>
+      <c r="M169">
+        <v>6</v>
+      </c>
+      <c r="N169" t="s">
+        <v>29</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>18</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>67</v>
+      </c>
+      <c r="R169">
+        <v>58</v>
+      </c>
+      <c r="S169">
+        <v>310.34482800000001</v>
+      </c>
+      <c r="T169">
+        <v>3</v>
+      </c>
+      <c r="V169">
+        <v>6</v>
+      </c>
+      <c r="W169">
+        <v>5.1724139999999998</v>
+      </c>
+      <c r="X169">
+        <v>4</v>
+      </c>
+      <c r="Y169">
+        <v>6.8965519999999998</v>
+      </c>
+      <c r="Z169">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>38</v>
+      </c>
+      <c r="B170" t="s">
+        <v>37</v>
+      </c>
+      <c r="C170" t="s">
+        <v>91</v>
+      </c>
+      <c r="D170" t="s">
+        <v>35</v>
+      </c>
+      <c r="E170" t="s">
+        <v>41</v>
+      </c>
+      <c r="F170" t="s">
+        <v>33</v>
+      </c>
+      <c r="G170" t="s">
+        <v>32</v>
+      </c>
+      <c r="H170" t="s">
+        <v>31</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170" t="s">
+        <v>30</v>
+      </c>
+      <c r="K170">
+        <v>16</v>
+      </c>
+      <c r="L170">
+        <v>1.3125</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170" t="s">
+        <v>29</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>1</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>67</v>
+      </c>
+      <c r="R170">
+        <v>21</v>
+      </c>
+      <c r="S170">
+        <v>47.619047999999999</v>
+      </c>
+      <c r="T170">
+        <v>1</v>
+      </c>
+      <c r="V170">
+        <v>1</v>
+      </c>
+      <c r="W170">
+        <v>4.7619049999999996</v>
+      </c>
+      <c r="X170">
+        <v>1</v>
+      </c>
+      <c r="Y170">
+        <v>4.7619049999999996</v>
+      </c>
+      <c r="Z170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>38</v>
+      </c>
+      <c r="B171" t="s">
+        <v>37</v>
+      </c>
+      <c r="C171" t="s">
+        <v>91</v>
+      </c>
+      <c r="D171" t="s">
+        <v>35</v>
+      </c>
+      <c r="E171" t="s">
+        <v>40</v>
+      </c>
+      <c r="F171" t="s">
+        <v>33</v>
+      </c>
+      <c r="G171" t="s">
+        <v>32</v>
+      </c>
+      <c r="H171" t="s">
+        <v>31</v>
+      </c>
+      <c r="I171">
+        <v>3</v>
+      </c>
+      <c r="J171" t="s">
+        <v>30</v>
+      </c>
+      <c r="K171">
+        <v>92</v>
+      </c>
+      <c r="L171">
+        <v>1.2173909999999999</v>
+      </c>
+      <c r="M171">
+        <v>20</v>
+      </c>
+      <c r="N171" t="s">
+        <v>29</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>60</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>67</v>
+      </c>
+      <c r="R171">
+        <v>112</v>
+      </c>
+      <c r="S171">
+        <v>535.71428600000002</v>
+      </c>
+      <c r="T171">
+        <v>3</v>
+      </c>
+      <c r="V171">
+        <v>20</v>
+      </c>
+      <c r="W171">
+        <v>2.6785709999999998</v>
+      </c>
+      <c r="X171">
+        <v>4</v>
+      </c>
+      <c r="Y171">
+        <v>3.5714290000000002</v>
+      </c>
+      <c r="Z171">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>38</v>
+      </c>
+      <c r="B172" t="s">
+        <v>37</v>
+      </c>
+      <c r="C172" t="s">
+        <v>91</v>
+      </c>
+      <c r="D172" t="s">
+        <v>35</v>
+      </c>
+      <c r="E172" t="s">
+        <v>34</v>
+      </c>
+      <c r="F172" t="s">
+        <v>33</v>
+      </c>
+      <c r="G172" t="s">
+        <v>32</v>
+      </c>
+      <c r="H172" t="s">
+        <v>31</v>
+      </c>
+      <c r="I172">
+        <v>562</v>
+      </c>
+      <c r="J172" t="s">
+        <v>30</v>
+      </c>
+      <c r="K172">
+        <v>6412</v>
+      </c>
+      <c r="L172">
+        <v>1.4909539999999999</v>
+      </c>
+      <c r="M172">
+        <v>9.0462633500000003</v>
+      </c>
+      <c r="N172" t="s">
+        <v>29</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>5084</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>67</v>
+      </c>
+      <c r="R172">
+        <v>9560</v>
+      </c>
+      <c r="S172">
+        <v>531.79916300000002</v>
+      </c>
+      <c r="T172">
+        <v>562</v>
+      </c>
+      <c r="V172">
+        <v>9.0462629999999997</v>
+      </c>
+      <c r="W172">
+        <v>5.8786610000000001</v>
+      </c>
+      <c r="X172">
+        <v>617</v>
+      </c>
+      <c r="Y172">
+        <v>6.4539749999999998</v>
+      </c>
+      <c r="Z172">
+        <v>8.2398699999999998</v>
+      </c>
+    </row>
+    <row r="173" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>38</v>
+      </c>
+      <c r="B173" t="s">
+        <v>37</v>
+      </c>
+      <c r="C173" t="s">
+        <v>91</v>
+      </c>
+      <c r="D173" t="s">
+        <v>35</v>
+      </c>
+      <c r="E173" t="s">
+        <v>34</v>
+      </c>
+      <c r="F173" t="s">
+        <v>46</v>
+      </c>
+      <c r="G173" t="s">
+        <v>32</v>
+      </c>
+      <c r="H173" t="s">
+        <v>31</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="N173" t="s">
+        <v>29</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>67</v>
+      </c>
+      <c r="R173">
+        <v>2</v>
+      </c>
+      <c r="S173">
+        <v>0</v>
+      </c>
+      <c r="X173">
+        <v>0</v>
+      </c>
+      <c r="Y173">
+        <v>0</v>
+      </c>
+      <c r="Z173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>38</v>
+      </c>
+      <c r="B174" t="s">
+        <v>37</v>
+      </c>
+      <c r="C174" t="s">
+        <v>92</v>
+      </c>
+      <c r="D174" t="s">
+        <v>35</v>
+      </c>
+      <c r="E174" t="s">
+        <v>43</v>
+      </c>
+      <c r="F174" t="s">
+        <v>33</v>
+      </c>
+      <c r="G174" t="s">
+        <v>32</v>
+      </c>
+      <c r="H174" t="s">
+        <v>31</v>
+      </c>
+      <c r="I174">
+        <v>71</v>
+      </c>
+      <c r="J174" t="s">
+        <v>30</v>
+      </c>
+      <c r="K174">
+        <v>2148</v>
+      </c>
+      <c r="L174">
+        <v>1.6378029999999999</v>
+      </c>
+      <c r="M174">
+        <v>20.957746480000001</v>
+      </c>
+      <c r="N174" t="s">
+        <v>29</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <v>1488</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>67</v>
+      </c>
+      <c r="R174">
+        <v>3518</v>
+      </c>
+      <c r="S174">
+        <v>422.96759500000002</v>
+      </c>
+      <c r="T174">
+        <v>71</v>
+      </c>
+      <c r="V174">
+        <v>20.957746</v>
+      </c>
+      <c r="W174">
+        <v>2.018192</v>
+      </c>
+      <c r="X174">
+        <v>75</v>
+      </c>
+      <c r="Y174">
+        <v>2.1318929999999998</v>
+      </c>
+      <c r="Z174">
+        <v>19.84</v>
+      </c>
+    </row>
+    <row r="175" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>38</v>
+      </c>
+      <c r="B175" t="s">
+        <v>37</v>
+      </c>
+      <c r="C175" t="s">
+        <v>92</v>
+      </c>
+      <c r="D175" t="s">
+        <v>35</v>
+      </c>
+      <c r="E175" t="s">
+        <v>43</v>
+      </c>
+      <c r="F175" t="s">
+        <v>46</v>
+      </c>
+      <c r="G175" t="s">
+        <v>32</v>
+      </c>
+      <c r="H175" t="s">
+        <v>31</v>
+      </c>
+      <c r="K175">
+        <v>6</v>
+      </c>
+      <c r="L175">
+        <v>1.6666669999999999</v>
+      </c>
+      <c r="N175" t="s">
+        <v>29</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="P175">
+        <v>3</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>67</v>
+      </c>
+      <c r="R175">
+        <v>10</v>
+      </c>
+      <c r="S175">
+        <v>300</v>
+      </c>
+      <c r="X175">
+        <v>0</v>
+      </c>
+      <c r="Y175">
+        <v>0</v>
+      </c>
+      <c r="Z175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>38</v>
+      </c>
+      <c r="B176" t="s">
+        <v>37</v>
+      </c>
+      <c r="C176" t="s">
+        <v>92</v>
+      </c>
+      <c r="D176" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176" t="s">
+        <v>42</v>
+      </c>
+      <c r="F176" t="s">
+        <v>33</v>
+      </c>
+      <c r="G176" t="s">
+        <v>32</v>
+      </c>
+      <c r="H176" t="s">
+        <v>31</v>
+      </c>
+      <c r="I176">
+        <v>3</v>
+      </c>
+      <c r="J176" t="s">
+        <v>30</v>
+      </c>
+      <c r="K176">
+        <v>136</v>
+      </c>
+      <c r="L176">
+        <v>1.3382350000000001</v>
+      </c>
+      <c r="M176">
+        <v>18.333333329999999</v>
+      </c>
+      <c r="N176" t="s">
+        <v>29</v>
+      </c>
+      <c r="O176">
+        <v>0</v>
+      </c>
+      <c r="P176">
+        <v>55</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>67</v>
+      </c>
+      <c r="R176">
+        <v>182</v>
+      </c>
+      <c r="S176">
+        <v>302.19780200000002</v>
+      </c>
+      <c r="T176">
+        <v>3</v>
+      </c>
+      <c r="V176">
+        <v>18.333333</v>
+      </c>
+      <c r="W176">
+        <v>1.648352</v>
+      </c>
+      <c r="X176">
+        <v>3</v>
+      </c>
+      <c r="Y176">
+        <v>1.648352</v>
+      </c>
+      <c r="Z176">
+        <v>18.333333</v>
+      </c>
+    </row>
+    <row r="177" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>38</v>
+      </c>
+      <c r="B177" t="s">
+        <v>37</v>
+      </c>
+      <c r="C177" t="s">
+        <v>92</v>
+      </c>
+      <c r="D177" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" t="s">
+        <v>40</v>
+      </c>
+      <c r="F177" t="s">
+        <v>33</v>
+      </c>
+      <c r="G177" t="s">
+        <v>32</v>
+      </c>
+      <c r="H177" t="s">
+        <v>31</v>
+      </c>
+      <c r="I177">
+        <v>155</v>
+      </c>
+      <c r="J177" t="s">
+        <v>30</v>
+      </c>
+      <c r="K177">
+        <v>3852</v>
+      </c>
+      <c r="L177">
+        <v>1.501298</v>
+      </c>
+      <c r="M177">
+        <v>20.838709680000001</v>
+      </c>
+      <c r="N177" t="s">
+        <v>29</v>
+      </c>
+      <c r="O177">
+        <v>0</v>
+      </c>
+      <c r="P177">
+        <v>3230</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>67</v>
+      </c>
+      <c r="R177">
+        <v>5783</v>
+      </c>
+      <c r="S177">
+        <v>558.53363300000001</v>
+      </c>
+      <c r="T177">
+        <v>155</v>
+      </c>
+      <c r="V177">
+        <v>20.838709999999999</v>
+      </c>
+      <c r="W177">
+        <v>2.6802700000000002</v>
+      </c>
+      <c r="X177">
+        <v>208</v>
+      </c>
+      <c r="Y177">
+        <v>3.596749</v>
+      </c>
+      <c r="Z177">
+        <v>15.528846</v>
+      </c>
+    </row>
+    <row r="178" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>38</v>
+      </c>
+      <c r="B178" t="s">
+        <v>37</v>
+      </c>
+      <c r="C178" t="s">
+        <v>92</v>
+      </c>
+      <c r="D178" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" t="s">
+        <v>34</v>
+      </c>
+      <c r="F178" t="s">
+        <v>33</v>
+      </c>
+      <c r="G178" t="s">
+        <v>32</v>
+      </c>
+      <c r="H178" t="s">
+        <v>31</v>
+      </c>
+      <c r="I178">
+        <v>52</v>
+      </c>
+      <c r="J178" t="s">
+        <v>30</v>
+      </c>
+      <c r="K178">
+        <v>904</v>
+      </c>
+      <c r="L178">
+        <v>1.5730090000000001</v>
+      </c>
+      <c r="M178">
+        <v>20.40384615</v>
+      </c>
+      <c r="N178" t="s">
+        <v>29</v>
+      </c>
+      <c r="O178">
+        <v>0</v>
+      </c>
+      <c r="P178">
+        <v>1061</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>67</v>
+      </c>
+      <c r="R178">
+        <v>1422</v>
+      </c>
+      <c r="S178">
+        <v>746.13220799999999</v>
+      </c>
+      <c r="T178">
+        <v>52</v>
+      </c>
+      <c r="V178">
+        <v>20.403846000000001</v>
+      </c>
+      <c r="W178">
+        <v>3.6568209999999999</v>
+      </c>
+      <c r="X178">
+        <v>57</v>
+      </c>
+      <c r="Y178">
+        <v>4.0084390000000001</v>
+      </c>
+      <c r="Z178">
+        <v>18.614035000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>38</v>
+      </c>
+      <c r="B179" t="s">
+        <v>37</v>
+      </c>
+      <c r="C179" t="s">
+        <v>92</v>
+      </c>
+      <c r="D179" t="s">
+        <v>35</v>
+      </c>
+      <c r="E179" t="s">
+        <v>34</v>
+      </c>
+      <c r="F179" t="s">
+        <v>46</v>
+      </c>
+      <c r="G179" t="s">
+        <v>32</v>
+      </c>
+      <c r="H179" t="s">
+        <v>31</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="N179" t="s">
+        <v>29</v>
+      </c>
+      <c r="O179">
+        <v>0</v>
+      </c>
+      <c r="P179">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>67</v>
+      </c>
+      <c r="R179">
+        <v>3</v>
+      </c>
+      <c r="S179">
+        <v>0</v>
+      </c>
+      <c r="X179">
+        <v>0</v>
+      </c>
+      <c r="Y179">
+        <v>0</v>
+      </c>
+      <c r="Z179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>38</v>
+      </c>
+      <c r="B180" t="s">
+        <v>37</v>
+      </c>
+      <c r="C180" t="s">
+        <v>93</v>
+      </c>
+      <c r="D180" t="s">
+        <v>35</v>
+      </c>
+      <c r="E180" t="s">
+        <v>43</v>
+      </c>
+      <c r="F180" t="s">
+        <v>33</v>
+      </c>
+      <c r="G180" t="s">
+        <v>32</v>
+      </c>
+      <c r="H180" t="s">
+        <v>31</v>
+      </c>
+      <c r="I180">
+        <v>143</v>
+      </c>
+      <c r="J180" t="s">
+        <v>30</v>
+      </c>
+      <c r="K180">
+        <v>3934</v>
+      </c>
+      <c r="L180">
+        <v>1.684291</v>
+      </c>
+      <c r="M180">
+        <v>22.18181818</v>
+      </c>
+      <c r="N180" t="s">
+        <v>29</v>
+      </c>
+      <c r="O180">
+        <v>0</v>
+      </c>
+      <c r="P180">
+        <v>3172</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>67</v>
+      </c>
+      <c r="R180">
+        <v>6626</v>
+      </c>
+      <c r="S180">
+        <v>478.72019299999999</v>
+      </c>
+      <c r="T180">
+        <v>143</v>
+      </c>
+      <c r="V180">
+        <v>22.181818</v>
+      </c>
+      <c r="W180">
+        <v>2.1581649999999999</v>
+      </c>
+      <c r="X180">
+        <v>183</v>
+      </c>
+      <c r="Y180">
+        <v>2.7618469999999999</v>
+      </c>
+      <c r="Z180">
+        <v>17.333333</v>
+      </c>
+    </row>
+    <row r="181" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>38</v>
+      </c>
+      <c r="B181" t="s">
+        <v>37</v>
+      </c>
+      <c r="C181" t="s">
+        <v>93</v>
+      </c>
+      <c r="D181" t="s">
+        <v>35</v>
+      </c>
+      <c r="E181" t="s">
+        <v>43</v>
+      </c>
+      <c r="F181" t="s">
+        <v>46</v>
+      </c>
+      <c r="G181" t="s">
+        <v>32</v>
+      </c>
+      <c r="H181" t="s">
+        <v>31</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="N181" t="s">
+        <v>29</v>
+      </c>
+      <c r="O181">
+        <v>0</v>
+      </c>
+      <c r="P181">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>67</v>
+      </c>
+      <c r="R181">
+        <v>2</v>
+      </c>
+      <c r="S181">
+        <v>0</v>
+      </c>
+      <c r="X181">
+        <v>0</v>
+      </c>
+      <c r="Y181">
+        <v>0</v>
+      </c>
+      <c r="Z181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>38</v>
+      </c>
+      <c r="B182" t="s">
+        <v>37</v>
+      </c>
+      <c r="C182" t="s">
+        <v>93</v>
+      </c>
+      <c r="D182" t="s">
+        <v>35</v>
+      </c>
+      <c r="E182" t="s">
+        <v>42</v>
+      </c>
+      <c r="F182" t="s">
+        <v>33</v>
+      </c>
+      <c r="G182" t="s">
+        <v>32</v>
+      </c>
+      <c r="H182" t="s">
+        <v>31</v>
+      </c>
+      <c r="I182">
+        <v>24</v>
+      </c>
+      <c r="J182" t="s">
+        <v>30</v>
+      </c>
+      <c r="K182">
+        <v>702</v>
+      </c>
+      <c r="L182">
+        <v>1.480057</v>
+      </c>
+      <c r="M182">
+        <v>15.58333333</v>
+      </c>
+      <c r="N182" t="s">
+        <v>29</v>
+      </c>
+      <c r="O182">
+        <v>0</v>
+      </c>
+      <c r="P182">
+        <v>374</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>67</v>
+      </c>
+      <c r="R182">
+        <v>1039</v>
+      </c>
+      <c r="S182">
+        <v>359.961501</v>
+      </c>
+      <c r="T182">
+        <v>24</v>
+      </c>
+      <c r="V182">
+        <v>15.583333</v>
+      </c>
+      <c r="W182">
+        <v>2.3099129999999999</v>
+      </c>
+      <c r="X182">
+        <v>31</v>
+      </c>
+      <c r="Y182">
+        <v>2.983638</v>
+      </c>
+      <c r="Z182">
+        <v>12.064515999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>38</v>
+      </c>
+      <c r="B183" t="s">
+        <v>37</v>
+      </c>
+      <c r="C183" t="s">
+        <v>93</v>
+      </c>
+      <c r="D183" t="s">
+        <v>35</v>
+      </c>
+      <c r="E183" t="s">
+        <v>41</v>
+      </c>
+      <c r="F183" t="s">
+        <v>33</v>
+      </c>
+      <c r="G183" t="s">
+        <v>32</v>
+      </c>
+      <c r="H183" t="s">
+        <v>31</v>
+      </c>
+      <c r="K183">
+        <v>16</v>
+      </c>
+      <c r="L183">
+        <v>1.25</v>
+      </c>
+      <c r="N183" t="s">
+        <v>29</v>
+      </c>
+      <c r="O183">
+        <v>0</v>
+      </c>
+      <c r="P183">
+        <v>1</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>67</v>
+      </c>
+      <c r="R183">
+        <v>20</v>
+      </c>
+      <c r="S183">
+        <v>50</v>
+      </c>
+      <c r="X183">
+        <v>0</v>
+      </c>
+      <c r="Y183">
+        <v>0</v>
+      </c>
+      <c r="Z183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>38</v>
+      </c>
+      <c r="B184" t="s">
+        <v>37</v>
+      </c>
+      <c r="C184" t="s">
+        <v>93</v>
+      </c>
+      <c r="D184" t="s">
+        <v>35</v>
+      </c>
+      <c r="E184" t="s">
+        <v>40</v>
+      </c>
+      <c r="F184" t="s">
+        <v>33</v>
+      </c>
+      <c r="G184" t="s">
+        <v>32</v>
+      </c>
+      <c r="H184" t="s">
+        <v>31</v>
+      </c>
+      <c r="K184">
+        <v>234</v>
+      </c>
+      <c r="L184">
+        <v>1.2863249999999999</v>
+      </c>
+      <c r="N184" t="s">
+        <v>29</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+      <c r="P184">
+        <v>159</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>67</v>
+      </c>
+      <c r="R184">
+        <v>301</v>
+      </c>
+      <c r="S184">
+        <v>528.23920299999997</v>
+      </c>
+      <c r="X184">
+        <v>8</v>
+      </c>
+      <c r="Y184">
+        <v>2.657807</v>
+      </c>
+      <c r="Z184">
+        <v>19.875</v>
+      </c>
+    </row>
+    <row r="185" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>38</v>
+      </c>
+      <c r="B185" t="s">
+        <v>37</v>
+      </c>
+      <c r="C185" t="s">
+        <v>93</v>
+      </c>
+      <c r="D185" t="s">
+        <v>35</v>
+      </c>
+      <c r="E185" t="s">
+        <v>34</v>
+      </c>
+      <c r="F185" t="s">
+        <v>33</v>
+      </c>
+      <c r="G185" t="s">
+        <v>32</v>
+      </c>
+      <c r="H185" t="s">
+        <v>31</v>
+      </c>
+      <c r="I185">
+        <v>114</v>
+      </c>
+      <c r="J185" t="s">
+        <v>30</v>
+      </c>
+      <c r="K185">
+        <v>1398</v>
+      </c>
+      <c r="L185">
+        <v>1.7153080000000001</v>
+      </c>
+      <c r="M185">
+        <v>19.1754386</v>
+      </c>
+      <c r="N185" t="s">
+        <v>29</v>
+      </c>
+      <c r="O185">
+        <v>0</v>
+      </c>
+      <c r="P185">
+        <v>2186</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>67</v>
+      </c>
+      <c r="R185">
+        <v>2398</v>
+      </c>
+      <c r="S185">
+        <v>911.59299399999998</v>
+      </c>
+      <c r="T185">
+        <v>114</v>
+      </c>
+      <c r="V185">
+        <v>19.175439000000001</v>
+      </c>
+      <c r="W185">
+        <v>4.7539619999999996</v>
+      </c>
+      <c r="X185">
+        <v>151</v>
+      </c>
+      <c r="Y185">
+        <v>6.2969140000000001</v>
+      </c>
+      <c r="Z185">
+        <v>14.476820999999999</v>
+      </c>
+    </row>
+    <row r="186" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>38</v>
+      </c>
+      <c r="B186" t="s">
+        <v>37</v>
+      </c>
+      <c r="C186" t="s">
+        <v>94</v>
+      </c>
+      <c r="D186" t="s">
+        <v>35</v>
+      </c>
+      <c r="E186" t="s">
+        <v>43</v>
+      </c>
+      <c r="F186" t="s">
+        <v>33</v>
+      </c>
+      <c r="G186" t="s">
+        <v>32</v>
+      </c>
+      <c r="H186" t="s">
+        <v>31</v>
+      </c>
+      <c r="I186">
+        <v>81</v>
+      </c>
+      <c r="J186" t="s">
+        <v>30</v>
+      </c>
+      <c r="K186">
+        <v>1778</v>
+      </c>
+      <c r="L186">
+        <v>1.4308209999999999</v>
+      </c>
+      <c r="M186">
+        <v>16.333333329999999</v>
+      </c>
+      <c r="N186" t="s">
+        <v>29</v>
+      </c>
+      <c r="O186">
+        <v>0</v>
+      </c>
+      <c r="P186">
+        <v>1323</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>62</v>
+      </c>
+      <c r="R186">
+        <v>2544</v>
+      </c>
+      <c r="S186">
+        <v>520.04717000000005</v>
+      </c>
+      <c r="T186">
+        <v>81</v>
+      </c>
+      <c r="V186">
+        <v>16.333333</v>
+      </c>
+      <c r="W186">
+        <v>3.1839620000000002</v>
+      </c>
+      <c r="X186">
+        <v>86</v>
+      </c>
+      <c r="Y186">
+        <v>3.380503</v>
+      </c>
+      <c r="Z186">
+        <v>15.383721</v>
+      </c>
+    </row>
+    <row r="187" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>38</v>
+      </c>
+      <c r="B187" t="s">
+        <v>37</v>
+      </c>
+      <c r="C187" t="s">
+        <v>94</v>
+      </c>
+      <c r="D187" t="s">
+        <v>35</v>
+      </c>
+      <c r="E187" t="s">
+        <v>43</v>
+      </c>
+      <c r="F187" t="s">
+        <v>46</v>
+      </c>
+      <c r="G187" t="s">
+        <v>32</v>
+      </c>
+      <c r="H187" t="s">
+        <v>31</v>
+      </c>
+      <c r="K187">
+        <v>2</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="N187" t="s">
+        <v>29</v>
+      </c>
+      <c r="O187">
+        <v>0</v>
+      </c>
+      <c r="P187">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>62</v>
+      </c>
+      <c r="R187">
+        <v>2</v>
+      </c>
+      <c r="S187">
+        <v>0</v>
+      </c>
+      <c r="X187">
+        <v>0</v>
+      </c>
+      <c r="Y187">
+        <v>0</v>
+      </c>
+      <c r="Z187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>38</v>
+      </c>
+      <c r="B188" t="s">
+        <v>37</v>
+      </c>
+      <c r="C188" t="s">
+        <v>94</v>
+      </c>
+      <c r="D188" t="s">
+        <v>35</v>
+      </c>
+      <c r="E188" t="s">
+        <v>42</v>
+      </c>
+      <c r="F188" t="s">
+        <v>33</v>
+      </c>
+      <c r="G188" t="s">
+        <v>32</v>
+      </c>
+      <c r="H188" t="s">
+        <v>31</v>
+      </c>
+      <c r="I188">
+        <v>3</v>
+      </c>
+      <c r="J188" t="s">
+        <v>30</v>
+      </c>
+      <c r="K188">
+        <v>120</v>
+      </c>
+      <c r="L188">
+        <v>1.375</v>
+      </c>
+      <c r="M188">
+        <v>19.666666670000001</v>
+      </c>
+      <c r="N188" t="s">
+        <v>29</v>
+      </c>
+      <c r="O188">
+        <v>0</v>
+      </c>
+      <c r="P188">
+        <v>59</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>62</v>
+      </c>
+      <c r="R188">
+        <v>165</v>
+      </c>
+      <c r="S188">
+        <v>357.57575800000001</v>
+      </c>
+      <c r="T188">
+        <v>3</v>
+      </c>
+      <c r="V188">
+        <v>19.666667</v>
+      </c>
+      <c r="W188">
+        <v>1.818182</v>
+      </c>
+      <c r="X188">
+        <v>3</v>
+      </c>
+      <c r="Y188">
+        <v>1.818182</v>
+      </c>
+      <c r="Z188">
+        <v>19.666667</v>
+      </c>
+    </row>
+    <row r="189" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>38</v>
+      </c>
+      <c r="B189" t="s">
+        <v>37</v>
+      </c>
+      <c r="C189" t="s">
+        <v>94</v>
+      </c>
+      <c r="D189" t="s">
+        <v>35</v>
+      </c>
+      <c r="E189" t="s">
+        <v>40</v>
+      </c>
+      <c r="F189" t="s">
+        <v>33</v>
+      </c>
+      <c r="G189" t="s">
+        <v>32</v>
+      </c>
+      <c r="H189" t="s">
+        <v>31</v>
+      </c>
+      <c r="I189">
+        <v>178</v>
+      </c>
+      <c r="J189" t="s">
+        <v>30</v>
+      </c>
+      <c r="K189">
+        <v>3450</v>
+      </c>
+      <c r="L189">
+        <v>1.416812</v>
+      </c>
+      <c r="M189">
+        <v>14.719101119999999</v>
+      </c>
+      <c r="N189" t="s">
+        <v>29</v>
+      </c>
+      <c r="O189">
+        <v>0</v>
+      </c>
+      <c r="P189">
+        <v>2620</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>62</v>
+      </c>
+      <c r="R189">
+        <v>4888</v>
+      </c>
+      <c r="S189">
+        <v>536.00654699999996</v>
+      </c>
+      <c r="T189">
+        <v>178</v>
+      </c>
+      <c r="V189">
+        <v>14.719101</v>
+      </c>
+      <c r="W189">
+        <v>3.6415709999999999</v>
+      </c>
+      <c r="X189">
+        <v>219</v>
+      </c>
+      <c r="Y189">
+        <v>4.4803600000000001</v>
+      </c>
+      <c r="Z189">
+        <v>11.963469999999999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>38</v>
+      </c>
+      <c r="B190" t="s">
+        <v>37</v>
+      </c>
+      <c r="C190" t="s">
+        <v>94</v>
+      </c>
+      <c r="D190" t="s">
+        <v>35</v>
+      </c>
+      <c r="E190" t="s">
+        <v>34</v>
+      </c>
+      <c r="F190" t="s">
+        <v>33</v>
+      </c>
+      <c r="G190" t="s">
+        <v>32</v>
+      </c>
+      <c r="H190" t="s">
+        <v>31</v>
+      </c>
+      <c r="I190">
+        <v>132</v>
+      </c>
+      <c r="J190" t="s">
+        <v>30</v>
+      </c>
+      <c r="K190">
+        <v>1630</v>
+      </c>
+      <c r="L190">
+        <v>1.456442</v>
+      </c>
+      <c r="M190">
+        <v>13.8030303</v>
+      </c>
+      <c r="N190" t="s">
+        <v>29</v>
+      </c>
+      <c r="O190">
+        <v>0</v>
+      </c>
+      <c r="P190">
+        <v>1822</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>62</v>
+      </c>
+      <c r="R190">
+        <v>2374</v>
+      </c>
+      <c r="S190">
+        <v>767.48104499999999</v>
+      </c>
+      <c r="T190">
+        <v>132</v>
+      </c>
+      <c r="V190">
+        <v>13.80303</v>
+      </c>
+      <c r="W190">
+        <v>5.5602359999999997</v>
+      </c>
+      <c r="X190">
+        <v>139</v>
+      </c>
+      <c r="Y190">
+        <v>5.8550969999999998</v>
+      </c>
+      <c r="Z190">
+        <v>13.107913999999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>38</v>
+      </c>
+      <c r="B191" t="s">
+        <v>37</v>
+      </c>
+      <c r="C191" t="s">
+        <v>94</v>
+      </c>
+      <c r="D191" t="s">
+        <v>35</v>
+      </c>
+      <c r="E191" t="s">
+        <v>34</v>
+      </c>
+      <c r="F191" t="s">
+        <v>46</v>
+      </c>
+      <c r="G191" t="s">
+        <v>32</v>
+      </c>
+      <c r="H191" t="s">
+        <v>31</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="N191" t="s">
+        <v>29</v>
+      </c>
+      <c r="O191">
+        <v>0</v>
+      </c>
+      <c r="P191">
+        <v>1</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>62</v>
+      </c>
+      <c r="R191">
+        <v>2</v>
+      </c>
+      <c r="S191">
+        <v>500</v>
+      </c>
+      <c r="X191">
+        <v>0</v>
+      </c>
+      <c r="Y191">
+        <v>0</v>
+      </c>
+      <c r="Z191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>38</v>
+      </c>
+      <c r="B192" t="s">
+        <v>37</v>
+      </c>
+      <c r="C192" t="s">
+        <v>95</v>
+      </c>
+      <c r="D192" t="s">
+        <v>35</v>
+      </c>
+      <c r="E192" t="s">
+        <v>43</v>
+      </c>
+      <c r="F192" t="s">
+        <v>70</v>
+      </c>
+      <c r="G192" t="s">
+        <v>32</v>
+      </c>
+      <c r="H192" t="s">
+        <v>31</v>
+      </c>
+      <c r="K192">
+        <v>11</v>
+      </c>
+      <c r="L192">
+        <v>1.0909089999999999</v>
+      </c>
+      <c r="N192">
+        <v>160</v>
+      </c>
+      <c r="O192" t="s">
+        <v>71</v>
+      </c>
+      <c r="P192">
+        <v>5</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>51</v>
+      </c>
+      <c r="R192">
+        <v>12</v>
+      </c>
+      <c r="S192">
+        <v>416.66666700000002</v>
+      </c>
+      <c r="X192">
+        <v>0</v>
+      </c>
+      <c r="Y192">
+        <v>0</v>
+      </c>
+      <c r="Z192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>38</v>
+      </c>
+      <c r="B193" t="s">
+        <v>37</v>
+      </c>
+      <c r="C193" t="s">
+        <v>95</v>
+      </c>
+      <c r="D193" t="s">
+        <v>35</v>
+      </c>
+      <c r="E193" t="s">
+        <v>43</v>
+      </c>
+      <c r="F193" t="s">
+        <v>33</v>
+      </c>
+      <c r="G193" t="s">
+        <v>32</v>
+      </c>
+      <c r="H193" t="s">
+        <v>31</v>
+      </c>
+      <c r="I193">
+        <v>221</v>
+      </c>
+      <c r="J193" t="s">
+        <v>30</v>
+      </c>
+      <c r="K193">
+        <v>2874</v>
+      </c>
+      <c r="L193">
+        <v>1.5330550000000001</v>
+      </c>
+      <c r="M193">
+        <v>11.53846154</v>
+      </c>
+      <c r="N193">
+        <v>160</v>
+      </c>
+      <c r="O193" t="s">
+        <v>71</v>
+      </c>
+      <c r="P193">
+        <v>2550</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>51</v>
+      </c>
+      <c r="R193">
+        <v>4406</v>
+      </c>
+      <c r="S193">
+        <v>578.75624100000005</v>
+      </c>
+      <c r="T193">
+        <v>221</v>
+      </c>
+      <c r="V193">
+        <v>11.538462000000001</v>
+      </c>
+      <c r="W193">
+        <v>5.0158870000000002</v>
+      </c>
+      <c r="X193">
+        <v>236</v>
+      </c>
+      <c r="Y193">
+        <v>5.3563320000000001</v>
+      </c>
+      <c r="Z193">
+        <v>10.805085</v>
+      </c>
+    </row>
+    <row r="194" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>38</v>
+      </c>
+      <c r="B194" t="s">
+        <v>37</v>
+      </c>
+      <c r="C194" t="s">
+        <v>95</v>
+      </c>
+      <c r="D194" t="s">
+        <v>35</v>
+      </c>
+      <c r="E194" t="s">
+        <v>42</v>
+      </c>
+      <c r="F194" t="s">
+        <v>33</v>
+      </c>
+      <c r="G194" t="s">
+        <v>32</v>
+      </c>
+      <c r="H194" t="s">
+        <v>31</v>
+      </c>
+      <c r="I194">
+        <v>8</v>
+      </c>
+      <c r="J194" t="s">
+        <v>30</v>
+      </c>
+      <c r="K194">
+        <v>298</v>
+      </c>
+      <c r="L194">
+        <v>1.2248319999999999</v>
+      </c>
+      <c r="M194">
+        <v>15.75</v>
+      </c>
+      <c r="N194">
+        <v>160</v>
+      </c>
+      <c r="O194" t="s">
+        <v>71</v>
+      </c>
+      <c r="P194">
+        <v>126</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>51</v>
+      </c>
+      <c r="R194">
+        <v>365</v>
+      </c>
+      <c r="S194">
+        <v>345.20547900000003</v>
+      </c>
+      <c r="T194">
+        <v>8</v>
+      </c>
+      <c r="V194">
+        <v>15.75</v>
+      </c>
+      <c r="W194">
+        <v>2.1917810000000002</v>
+      </c>
+      <c r="X194">
+        <v>8</v>
+      </c>
+      <c r="Y194">
+        <v>2.1917810000000002</v>
+      </c>
+      <c r="Z194">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="195" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>38</v>
+      </c>
+      <c r="B195" t="s">
+        <v>37</v>
+      </c>
+      <c r="C195" t="s">
+        <v>95</v>
+      </c>
+      <c r="D195" t="s">
+        <v>35</v>
+      </c>
+      <c r="E195" t="s">
+        <v>41</v>
+      </c>
+      <c r="F195" t="s">
+        <v>33</v>
+      </c>
+      <c r="G195" t="s">
+        <v>32</v>
+      </c>
+      <c r="H195" t="s">
+        <v>31</v>
+      </c>
+      <c r="I195">
+        <v>12</v>
+      </c>
+      <c r="J195" t="s">
+        <v>30</v>
+      </c>
+      <c r="K195">
+        <v>122</v>
+      </c>
+      <c r="L195">
+        <v>1.319672</v>
+      </c>
+      <c r="M195">
+        <v>2.3333333299999999</v>
+      </c>
+      <c r="N195">
+        <v>160</v>
+      </c>
+      <c r="O195" t="s">
+        <v>71</v>
+      </c>
+      <c r="P195">
+        <v>28</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>51</v>
+      </c>
+      <c r="R195">
+        <v>161</v>
+      </c>
+      <c r="S195">
+        <v>173.91304299999999</v>
+      </c>
+      <c r="T195">
+        <v>12</v>
+      </c>
+      <c r="V195">
+        <v>2.3333330000000001</v>
+      </c>
+      <c r="W195">
+        <v>7.4534159999999998</v>
+      </c>
+      <c r="X195">
+        <v>14</v>
+      </c>
+      <c r="Y195">
+        <v>8.6956520000000008</v>
+      </c>
+      <c r="Z195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>38</v>
+      </c>
+      <c r="B196" t="s">
+        <v>37</v>
+      </c>
+      <c r="C196" t="s">
+        <v>95</v>
+      </c>
+      <c r="D196" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196" t="s">
+        <v>40</v>
+      </c>
+      <c r="F196" t="s">
+        <v>33</v>
+      </c>
+      <c r="G196" t="s">
+        <v>32</v>
+      </c>
+      <c r="H196" t="s">
+        <v>31</v>
+      </c>
+      <c r="I196">
+        <v>45</v>
+      </c>
+      <c r="J196" t="s">
+        <v>30</v>
+      </c>
+      <c r="K196">
+        <v>566</v>
+      </c>
+      <c r="L196">
+        <v>1.3657239999999999</v>
+      </c>
+      <c r="M196">
+        <v>14.02222222</v>
+      </c>
+      <c r="N196">
+        <v>160</v>
+      </c>
+      <c r="O196" t="s">
+        <v>71</v>
+      </c>
+      <c r="P196">
+        <v>631</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>51</v>
+      </c>
+      <c r="R196">
+        <v>773</v>
+      </c>
+      <c r="S196">
+        <v>816.30012899999997</v>
+      </c>
+      <c r="T196">
+        <v>45</v>
+      </c>
+      <c r="V196">
+        <v>14.022221999999999</v>
+      </c>
+      <c r="W196">
+        <v>5.8214750000000004</v>
+      </c>
+      <c r="X196">
+        <v>59</v>
+      </c>
+      <c r="Y196">
+        <v>7.6326000000000001</v>
+      </c>
+      <c r="Z196">
+        <v>10.694915</v>
+      </c>
+    </row>
+    <row r="197" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>38</v>
+      </c>
+      <c r="B197" t="s">
+        <v>37</v>
+      </c>
+      <c r="C197" t="s">
+        <v>95</v>
+      </c>
+      <c r="D197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E197" t="s">
+        <v>34</v>
+      </c>
+      <c r="F197" t="s">
+        <v>33</v>
+      </c>
+      <c r="G197" t="s">
+        <v>32</v>
+      </c>
+      <c r="H197" t="s">
+        <v>31</v>
+      </c>
+      <c r="I197">
+        <v>125</v>
+      </c>
+      <c r="J197" t="s">
+        <v>30</v>
+      </c>
+      <c r="K197">
+        <v>1348</v>
+      </c>
+      <c r="L197">
+        <v>1.3456969999999999</v>
+      </c>
+      <c r="M197">
+        <v>12.776</v>
+      </c>
+      <c r="N197">
+        <v>160</v>
+      </c>
+      <c r="O197" t="s">
+        <v>71</v>
+      </c>
+      <c r="P197">
+        <v>1597</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>51</v>
+      </c>
+      <c r="R197">
+        <v>1814</v>
+      </c>
+      <c r="S197">
+        <v>880.37486200000001</v>
+      </c>
+      <c r="T197">
+        <v>125</v>
+      </c>
+      <c r="V197">
+        <v>12.776</v>
+      </c>
+      <c r="W197">
+        <v>6.8908490000000002</v>
+      </c>
+      <c r="X197">
+        <v>145</v>
+      </c>
+      <c r="Y197">
+        <v>7.993385</v>
+      </c>
+      <c r="Z197">
+        <v>11.013793</v>
+      </c>
+    </row>
+    <row r="198" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>38</v>
+      </c>
+      <c r="B198" t="s">
+        <v>37</v>
+      </c>
+      <c r="C198" t="s">
+        <v>96</v>
+      </c>
+      <c r="D198" t="s">
+        <v>35</v>
+      </c>
+      <c r="E198" t="s">
+        <v>43</v>
+      </c>
+      <c r="F198" t="s">
+        <v>33</v>
+      </c>
+      <c r="G198" t="s">
+        <v>97</v>
+      </c>
+      <c r="H198" t="s">
+        <v>31</v>
+      </c>
+      <c r="I198">
+        <v>1</v>
+      </c>
+      <c r="J198" t="s">
+        <v>30</v>
+      </c>
+      <c r="K198">
+        <v>39</v>
+      </c>
+      <c r="L198">
+        <v>1.0769230000000001</v>
+      </c>
+      <c r="M198">
+        <v>48</v>
+      </c>
+      <c r="N198">
+        <v>650</v>
+      </c>
+      <c r="O198" t="s">
+        <v>71</v>
+      </c>
+      <c r="P198">
+        <v>48</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>98</v>
+      </c>
+      <c r="R198">
+        <v>42</v>
+      </c>
+      <c r="S198">
+        <v>1142.857143</v>
+      </c>
+      <c r="T198">
+        <v>1</v>
+      </c>
+      <c r="V198">
+        <v>48</v>
+      </c>
+      <c r="W198">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="X198">
+        <v>1</v>
+      </c>
+      <c r="Y198">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="Z198">
+        <v>48</v>
+      </c>
+      <c r="AA198">
+        <v>1</v>
+      </c>
+      <c r="AB198">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="199" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>38</v>
+      </c>
+      <c r="B199" t="s">
+        <v>37</v>
+      </c>
+      <c r="C199" t="s">
+        <v>96</v>
+      </c>
+      <c r="D199" t="s">
+        <v>35</v>
+      </c>
+      <c r="E199" t="s">
+        <v>42</v>
+      </c>
+      <c r="F199" t="s">
+        <v>33</v>
+      </c>
+      <c r="G199" t="s">
+        <v>97</v>
+      </c>
+      <c r="H199" t="s">
+        <v>31</v>
+      </c>
+      <c r="K199">
+        <v>7</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="N199">
+        <v>650</v>
+      </c>
+      <c r="O199" t="s">
+        <v>71</v>
+      </c>
+      <c r="P199">
+        <v>2</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>98</v>
+      </c>
+      <c r="R199">
+        <v>7</v>
+      </c>
+      <c r="S199">
+        <v>285.71428600000002</v>
+      </c>
+      <c r="X199">
+        <v>0</v>
+      </c>
+      <c r="Y199">
+        <v>0</v>
+      </c>
+      <c r="Z199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>38</v>
+      </c>
+      <c r="B200" t="s">
+        <v>37</v>
+      </c>
+      <c r="C200" t="s">
+        <v>96</v>
+      </c>
+      <c r="D200" t="s">
+        <v>35</v>
+      </c>
+      <c r="E200" t="s">
+        <v>40</v>
+      </c>
+      <c r="F200" t="s">
+        <v>33</v>
+      </c>
+      <c r="G200" t="s">
+        <v>97</v>
+      </c>
+      <c r="H200" t="s">
+        <v>31</v>
+      </c>
+      <c r="K200">
+        <v>29</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>650</v>
+      </c>
+      <c r="O200" t="s">
+        <v>71</v>
+      </c>
+      <c r="P200">
+        <v>18</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>98</v>
+      </c>
+      <c r="R200">
+        <v>29</v>
+      </c>
+      <c r="S200">
+        <v>620.68965500000002</v>
+      </c>
+      <c r="X200">
+        <v>0</v>
+      </c>
+      <c r="Y200">
+        <v>0</v>
+      </c>
+      <c r="Z200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>38</v>
+      </c>
+      <c r="B201" t="s">
+        <v>37</v>
+      </c>
+      <c r="C201" t="s">
+        <v>96</v>
+      </c>
+      <c r="D201" t="s">
+        <v>35</v>
+      </c>
+      <c r="E201" t="s">
+        <v>34</v>
+      </c>
+      <c r="F201" t="s">
+        <v>33</v>
+      </c>
+      <c r="G201" t="s">
+        <v>97</v>
+      </c>
+      <c r="H201" t="s">
+        <v>31</v>
+      </c>
+      <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201" t="s">
+        <v>30</v>
+      </c>
+      <c r="K201">
+        <v>109</v>
+      </c>
+      <c r="L201">
+        <v>1.009174</v>
+      </c>
+      <c r="M201">
+        <v>86</v>
+      </c>
+      <c r="N201">
+        <v>650</v>
+      </c>
+      <c r="O201" t="s">
+        <v>71</v>
+      </c>
+      <c r="P201">
+        <v>172</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>98</v>
+      </c>
+      <c r="R201">
+        <v>110</v>
+      </c>
+      <c r="S201">
+        <v>1563.636364</v>
+      </c>
+      <c r="T201">
+        <v>2</v>
+      </c>
+      <c r="V201">
+        <v>86</v>
+      </c>
+      <c r="W201">
+        <v>1.818182</v>
+      </c>
+      <c r="X201">
+        <v>2</v>
+      </c>
+      <c r="Y201">
+        <v>1.818182</v>
+      </c>
+      <c r="Z201">
+        <v>86</v>
+      </c>
+      <c r="AA201">
+        <v>2</v>
+      </c>
+      <c r="AB201">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="202" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>38</v>
+      </c>
+      <c r="B202" t="s">
+        <v>37</v>
+      </c>
+      <c r="C202" t="s">
+        <v>99</v>
+      </c>
+      <c r="D202" t="s">
+        <v>35</v>
+      </c>
+      <c r="E202" t="s">
+        <v>43</v>
+      </c>
+      <c r="F202" t="s">
+        <v>33</v>
+      </c>
+      <c r="G202" t="s">
+        <v>32</v>
+      </c>
+      <c r="H202" t="s">
+        <v>31</v>
+      </c>
+      <c r="I202">
+        <v>16</v>
+      </c>
+      <c r="J202" t="s">
+        <v>30</v>
+      </c>
+      <c r="K202">
+        <v>895</v>
+      </c>
+      <c r="L202">
+        <v>1.118436</v>
+      </c>
+      <c r="M202">
+        <v>36.8125</v>
+      </c>
+      <c r="N202">
+        <v>160</v>
+      </c>
+      <c r="O202" t="s">
+        <v>71</v>
+      </c>
+      <c r="P202">
+        <v>589</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>100</v>
+      </c>
+      <c r="R202">
+        <v>1001</v>
+      </c>
+      <c r="S202">
+        <v>588.41158800000005</v>
+      </c>
+      <c r="T202">
+        <v>16</v>
+      </c>
+      <c r="V202">
+        <v>36.8125</v>
+      </c>
+      <c r="W202">
+        <v>1.5984020000000001</v>
+      </c>
+      <c r="X202">
+        <v>19</v>
+      </c>
+      <c r="Y202">
+        <v>1.898102</v>
+      </c>
+      <c r="Z202">
+        <v>31</v>
+      </c>
+      <c r="AA202">
+        <v>13</v>
+      </c>
+      <c r="AB202">
+        <v>45.307692000000003</v>
+      </c>
+    </row>
+    <row r="203" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>38</v>
+      </c>
+      <c r="B203" t="s">
+        <v>37</v>
+      </c>
+      <c r="C203" t="s">
+        <v>99</v>
+      </c>
+      <c r="D203" t="s">
+        <v>35</v>
+      </c>
+      <c r="E203" t="s">
+        <v>42</v>
+      </c>
+      <c r="F203" t="s">
+        <v>33</v>
+      </c>
+      <c r="G203" t="s">
+        <v>32</v>
+      </c>
+      <c r="H203" t="s">
+        <v>31</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+      <c r="J203" t="s">
+        <v>30</v>
+      </c>
+      <c r="K203">
+        <v>120</v>
+      </c>
+      <c r="L203">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M203">
+        <v>54</v>
+      </c>
+      <c r="N203">
+        <v>160</v>
+      </c>
+      <c r="O203" t="s">
+        <v>71</v>
+      </c>
+      <c r="P203">
+        <v>54</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>100</v>
+      </c>
+      <c r="R203">
+        <v>132</v>
+      </c>
+      <c r="S203">
+        <v>409.09090900000001</v>
+      </c>
+      <c r="T203">
+        <v>1</v>
+      </c>
+      <c r="V203">
+        <v>54</v>
+      </c>
+      <c r="W203">
+        <v>0.75757600000000003</v>
+      </c>
+      <c r="X203">
+        <v>1</v>
+      </c>
+      <c r="Y203">
+        <v>0.75757600000000003</v>
+      </c>
+      <c r="Z203">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="204" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>38</v>
+      </c>
+      <c r="B204" t="s">
+        <v>37</v>
+      </c>
+      <c r="C204" t="s">
+        <v>99</v>
+      </c>
+      <c r="D204" t="s">
+        <v>35</v>
+      </c>
+      <c r="E204" t="s">
+        <v>41</v>
+      </c>
+      <c r="F204" t="s">
+        <v>33</v>
+      </c>
+      <c r="G204" t="s">
+        <v>32</v>
+      </c>
+      <c r="H204" t="s">
+        <v>31</v>
+      </c>
+      <c r="K204">
+        <v>5</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>160</v>
+      </c>
+      <c r="O204" t="s">
+        <v>71</v>
+      </c>
+      <c r="P204">
+        <v>2</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>100</v>
+      </c>
+      <c r="R204">
+        <v>5</v>
+      </c>
+      <c r="S204">
+        <v>400</v>
+      </c>
+      <c r="X204">
+        <v>0</v>
+      </c>
+      <c r="Y204">
+        <v>0</v>
+      </c>
+      <c r="Z204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>38</v>
+      </c>
+      <c r="B205" t="s">
+        <v>37</v>
+      </c>
+      <c r="C205" t="s">
+        <v>99</v>
+      </c>
+      <c r="D205" t="s">
+        <v>35</v>
+      </c>
+      <c r="E205" t="s">
+        <v>40</v>
+      </c>
+      <c r="F205" t="s">
+        <v>33</v>
+      </c>
+      <c r="G205" t="s">
+        <v>32</v>
+      </c>
+      <c r="H205" t="s">
+        <v>31</v>
+      </c>
+      <c r="I205">
+        <v>2</v>
+      </c>
+      <c r="J205" t="s">
+        <v>30</v>
+      </c>
+      <c r="K205">
+        <v>279</v>
+      </c>
+      <c r="L205">
+        <v>1.064516</v>
+      </c>
+      <c r="M205">
+        <v>86</v>
+      </c>
+      <c r="N205">
+        <v>160</v>
+      </c>
+      <c r="O205" t="s">
+        <v>71</v>
+      </c>
+      <c r="P205">
+        <v>172</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>100</v>
+      </c>
+      <c r="R205">
+        <v>297</v>
+      </c>
+      <c r="S205">
+        <v>579.12457900000004</v>
+      </c>
+      <c r="T205">
+        <v>2</v>
+      </c>
+      <c r="V205">
+        <v>86</v>
+      </c>
+      <c r="W205">
+        <v>0.67340100000000003</v>
+      </c>
+      <c r="X205">
+        <v>2</v>
+      </c>
+      <c r="Y205">
+        <v>0.67340100000000003</v>
+      </c>
+      <c r="Z205">
+        <v>86</v>
+      </c>
+      <c r="AA205">
+        <v>2</v>
+      </c>
+      <c r="AB205">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="206" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>38</v>
+      </c>
+      <c r="B206" t="s">
+        <v>37</v>
+      </c>
+      <c r="C206" t="s">
+        <v>99</v>
+      </c>
+      <c r="D206" t="s">
+        <v>35</v>
+      </c>
+      <c r="E206" t="s">
+        <v>34</v>
+      </c>
+      <c r="F206" t="s">
+        <v>33</v>
+      </c>
+      <c r="G206" t="s">
+        <v>32</v>
+      </c>
+      <c r="H206" t="s">
+        <v>31</v>
+      </c>
+      <c r="I206">
+        <v>7</v>
+      </c>
+      <c r="J206" t="s">
+        <v>30</v>
+      </c>
+      <c r="K206">
+        <v>178</v>
+      </c>
+      <c r="L206">
+        <v>1.073034</v>
+      </c>
+      <c r="M206">
+        <v>29.85714286</v>
+      </c>
+      <c r="N206">
+        <v>160</v>
+      </c>
+      <c r="O206" t="s">
+        <v>71</v>
+      </c>
+      <c r="P206">
+        <v>209</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>100</v>
+      </c>
+      <c r="R206">
+        <v>191</v>
+      </c>
+      <c r="S206">
+        <v>1094.2408379999999</v>
+      </c>
+      <c r="T206">
+        <v>7</v>
+      </c>
+      <c r="V206">
+        <v>29.857143000000001</v>
+      </c>
+      <c r="W206">
+        <v>3.6649210000000001</v>
+      </c>
+      <c r="X206">
+        <v>9</v>
+      </c>
+      <c r="Y206">
+        <v>4.7120420000000003</v>
+      </c>
+      <c r="Z206">
+        <v>23.222221999999999</v>
+      </c>
+      <c r="AA206">
+        <v>8</v>
+      </c>
+      <c r="AB206">
+        <v>26.125</v>
       </c>
     </row>
   </sheetData>
